--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,11 +784,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>59</v>
+        <v>62.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>47.8</v>
       </c>
       <c r="R2" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -1036,12 +1040,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1060,11 +1064,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>57.4</v>
+        <v>61.1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>47.8</v>
       </c>
       <c r="R3" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -1292,7 +1300,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ronald Acuna</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1312,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>47.8</v>
       </c>
       <c r="R4" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1373,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1548,8 +1552,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -1568,7 +1580,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1588,12 +1600,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1612,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>52.2</v>
+        <v>56.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1636,10 +1648,10 @@
         <v>47.8</v>
       </c>
       <c r="R5" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1649,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1824,8 +1832,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -1864,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1888,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>51.9</v>
+        <v>55.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,7 +1918,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1912,10 +1928,10 @@
         <v>20</v>
       </c>
       <c r="R6" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
@@ -1925,39 +1941,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2100,8 +2112,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -2140,12 +2160,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2164,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.4</v>
+        <v>53</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,7 +2198,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2188,10 +2208,10 @@
         <v>47.8</v>
       </c>
       <c r="R7" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S7" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
@@ -2201,39 +2221,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2376,8 +2392,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -2391,24 +2415,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>547180</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -2416,31 +2440,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>44.6</v>
+        <v>49.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,65 +2478,61 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>49</v>
+        <v>34.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>47.8</v>
       </c>
       <c r="R8" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>32.5</v>
+        <v>24</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -2529,12 +2549,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2544,12 +2564,12 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 1 HR</t>
+          <t>Last 7 games: 3/19, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2559,101 +2579,109 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.6293</t>
+          <t>99.7248</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4843</t>
+          <t>0.3833</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2142</t>
+          <t>0.1477</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3757</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>30.91</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>27.39</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -2667,24 +2695,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>547180</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -2692,31 +2720,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.4</v>
+        <v>48.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,65 +2758,61 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>34.7</v>
+        <v>49</v>
       </c>
       <c r="Q9" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R9" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>24</v>
+        <v>32.5</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2805,12 +2829,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2820,12 +2844,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 1 HR</t>
+          <t>Last 7 games: 6/28, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2835,101 +2859,109 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>44.21</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>99.7248</t>
+          <t>101.6293</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.3833</t>
+          <t>0.4843</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1477</t>
+          <t>0.2142</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3757</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>38.47</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.219</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>27.39</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -2968,12 +3000,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2992,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>39.3</v>
+        <v>44.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3048,10 @@
         <v>20</v>
       </c>
       <c r="R10" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S10" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>78</v>
@@ -3029,39 +3061,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3204,8 +3232,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -3244,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.7</v>
+        <v>42.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,7 +3318,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3292,10 +3328,10 @@
         <v>20</v>
       </c>
       <c r="R11" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S11" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
         <v>78</v>
@@ -3305,39 +3341,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3480,8 +3512,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -3520,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3544,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38.4</v>
+        <v>42.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,7 +3598,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3568,10 +3608,10 @@
         <v>20</v>
       </c>
       <c r="R12" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T12" t="n">
         <v>78</v>
@@ -3581,39 +3621,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3756,8 +3792,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -3776,7 +3820,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3796,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3820,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>38</v>
+        <v>41.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,7 +3878,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3844,10 +3888,10 @@
         <v>47.8</v>
       </c>
       <c r="R13" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>50</v>
@@ -3857,39 +3901,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4032,8 +4072,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -4047,12 +4095,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>642086</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Dominic Smith</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4072,12 +4120,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4096,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>37.8</v>
+        <v>41</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,62 +4158,58 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>15.3</v>
+        <v>21.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>47.3</v>
+        <v>47.8</v>
       </c>
       <c r="R14" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4185,27 +4229,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 1/11, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4215,67 +4259,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.687</t>
+          <t>97.8111</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.384</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.1401</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2808</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>28.68</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.1309</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -4308,8 +4352,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -4323,12 +4375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>669016</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4348,12 +4400,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -4372,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>37.7</v>
+        <v>39.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,62 +4438,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>36.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q15" t="n">
         <v>20</v>
       </c>
       <c r="R15" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>35.6</v>
+        <v>40.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4461,22 +4509,22 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 1 HR</t>
+          <t>Contact streak: 9/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -4491,67 +4539,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>100.0232</t>
+          <t>98.4048</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4103</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1564</t>
+          <t>0.1383</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1525</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -4584,8 +4632,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -4599,24 +4655,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669221</t>
+          <t>650559</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sean Murphy</t>
+          <t>Bryan De La Cruz</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -4624,31 +4680,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>37.6</v>
+        <v>38.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,65 +4718,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>34</v>
+        <v>24.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R16" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4737,12 +4789,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4752,12 +4804,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Last 7 games: 2/17, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,101 +4819,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.19</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>101.2803</t>
+          <t>99.8033</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.3346</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2853</t>
+          <t>0.2828</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>70.92</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>16.37</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>25.37</t>
+          <t>19.87</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1456</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>27.39</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -4875,24 +4935,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -4900,31 +4960,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>36.9</v>
+        <v>38.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,65 +4998,61 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>25.2</v>
+        <v>15.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>47.3</v>
       </c>
       <c r="R17" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S17" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U17" t="n">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -5013,12 +5069,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5028,12 +5084,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Contact streak: 9/23 over last 7 games</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5043,101 +5099,109 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>98.4048</t>
+          <t>96.687</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1383</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.2808</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>27.39</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -5176,12 +5240,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5200,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>32.7</v>
+        <v>37.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,7 +5278,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -5224,10 +5288,10 @@
         <v>20</v>
       </c>
       <c r="R18" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
         <v>78</v>
@@ -5237,39 +5301,35 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5412,8 +5472,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -5452,12 +5520,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5476,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>25.1</v>
+        <v>28</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5500,10 +5568,10 @@
         <v>20</v>
       </c>
       <c r="R19" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>50</v>
@@ -5513,39 +5581,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -5688,8 +5752,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -6054,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6078,11 +6150,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>59</v>
+        <v>62.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -6092,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6174,10 @@
         <v>47.8</v>
       </c>
       <c r="R2" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -6115,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6290,8 +6358,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -6330,12 +6406,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -6354,11 +6430,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>57.4</v>
+        <v>61.1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -6368,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6454,10 @@
         <v>47.8</v>
       </c>
       <c r="R3" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6391,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6638,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -6586,7 +6666,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ronald Acuna</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6606,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6630,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6734,10 @@
         <v>47.8</v>
       </c>
       <c r="R4" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -6667,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6842,8 +6918,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -6862,7 +6946,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6882,12 +6966,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -6906,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>52.2</v>
+        <v>56.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -6930,10 +7014,10 @@
         <v>47.8</v>
       </c>
       <c r="R5" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -6943,39 +7027,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7118,8 +7198,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -7158,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7182,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>51.9</v>
+        <v>55.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,7 +7284,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7206,10 +7294,10 @@
         <v>20</v>
       </c>
       <c r="R6" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
@@ -7219,39 +7307,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7394,8 +7478,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -7434,12 +7526,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -7458,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.4</v>
+        <v>53</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,7 +7564,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -7482,10 +7574,10 @@
         <v>47.8</v>
       </c>
       <c r="R7" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S7" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
@@ -7495,39 +7587,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7670,8 +7758,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -7685,24 +7781,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>547180</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -7710,31 +7806,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>44.6</v>
+        <v>49.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,65 +7844,61 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>49</v>
+        <v>34.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>47.8</v>
       </c>
       <c r="R8" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>32.5</v>
+        <v>24</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -7823,12 +7915,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -7838,12 +7930,12 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 1 HR</t>
+          <t>Last 7 games: 3/19, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -7853,101 +7945,109 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.6293</t>
+          <t>99.7248</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4843</t>
+          <t>0.3833</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2142</t>
+          <t>0.1477</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3757</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>30.91</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>27.39</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -7961,24 +8061,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>547180</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -7986,31 +8086,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.4</v>
+        <v>48.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,65 +8124,61 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>34.7</v>
+        <v>49</v>
       </c>
       <c r="Q9" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R9" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>24</v>
+        <v>32.5</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -8099,12 +8195,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -8114,12 +8210,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 1 HR</t>
+          <t>Last 7 games: 6/28, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -8129,101 +8225,109 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>44.21</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>99.7248</t>
+          <t>101.6293</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.3833</t>
+          <t>0.4843</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1477</t>
+          <t>0.2142</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3757</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>38.47</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.219</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>27.39</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -8262,12 +8366,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8286,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>39.3</v>
+        <v>44.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8414,10 @@
         <v>20</v>
       </c>
       <c r="R10" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S10" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>78</v>
@@ -8323,39 +8427,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -8498,8 +8598,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -8538,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.7</v>
+        <v>42.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,7 +8684,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8586,10 +8694,10 @@
         <v>20</v>
       </c>
       <c r="R11" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S11" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
         <v>78</v>
@@ -8599,39 +8707,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -8774,8 +8878,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -8814,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8838,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38.4</v>
+        <v>42.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,7 +8964,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -8862,10 +8974,10 @@
         <v>20</v>
       </c>
       <c r="R12" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T12" t="n">
         <v>78</v>
@@ -8875,39 +8987,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9050,8 +9158,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -9070,7 +9186,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9090,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9114,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>38</v>
+        <v>41.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,7 +9244,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -9138,10 +9254,10 @@
         <v>47.8</v>
       </c>
       <c r="R13" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>50</v>
@@ -9151,39 +9267,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9326,8 +9438,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -9341,12 +9461,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>642086</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Dominic Smith</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9366,12 +9486,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9390,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>37.8</v>
+        <v>41</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,62 +9524,58 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>15.3</v>
+        <v>21.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>47.3</v>
+        <v>47.8</v>
       </c>
       <c r="R14" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9479,27 +9595,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 1/11, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9509,67 +9625,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.687</t>
+          <t>97.8111</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.384</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.1401</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2808</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>28.68</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.1309</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -9602,8 +9718,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -9617,12 +9741,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>669016</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9642,12 +9766,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -9666,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>37.7</v>
+        <v>39.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,62 +9804,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>36.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q15" t="n">
         <v>20</v>
       </c>
       <c r="R15" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>35.6</v>
+        <v>40.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9755,22 +9875,22 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 1 HR</t>
+          <t>Contact streak: 9/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -9785,67 +9905,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>100.0232</t>
+          <t>98.4048</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4103</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1564</t>
+          <t>0.1383</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1525</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -9878,8 +9998,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -9893,24 +10021,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669221</t>
+          <t>650559</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sean Murphy</t>
+          <t>Bryan De La Cruz</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -9918,31 +10046,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>37.6</v>
+        <v>38.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,65 +10084,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>34</v>
+        <v>24.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R16" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -10031,12 +10155,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10046,12 +10170,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Last 7 games: 2/17, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,101 +10185,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.19</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>101.2803</t>
+          <t>99.8033</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.3346</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2853</t>
+          <t>0.2828</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>70.92</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>16.37</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>25.37</t>
+          <t>19.87</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1456</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>27.39</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -10169,24 +10301,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -10194,31 +10326,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>36.9</v>
+        <v>38.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,65 +10364,61 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>25.2</v>
+        <v>15.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>47.3</v>
       </c>
       <c r="R17" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S17" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U17" t="n">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -10307,12 +10435,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -10322,12 +10450,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Contact streak: 9/23 over last 7 games</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10337,101 +10465,109 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>98.4048</t>
+          <t>96.687</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1383</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.2808</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>27.39</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -10470,12 +10606,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10494,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>32.7</v>
+        <v>37.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,7 +10644,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -10518,10 +10654,10 @@
         <v>20</v>
       </c>
       <c r="R18" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
         <v>78</v>
@@ -10531,39 +10667,35 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10706,8 +10838,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -10746,12 +10886,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -10770,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>25.1</v>
+        <v>28</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -10794,10 +10934,10 @@
         <v>20</v>
       </c>
       <c r="R19" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>50</v>
@@ -10807,39 +10947,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -10982,8 +11118,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Truist Park</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>56.2</v>
+        <v>57.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -1036,12 +1040,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>49.9</v>
+        <v>51.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>21.5</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -1312,12 +1320,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>47.3</v>
+        <v>48.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>21.5</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
@@ -1373,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1548,8 +1552,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -1588,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1612,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.5</v>
+        <v>46.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1636,10 +1648,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
@@ -1649,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1824,8 +1832,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -1864,12 +1880,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1888,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>42.9</v>
+        <v>41.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,7 +1918,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1912,10 +1928,10 @@
         <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
@@ -1925,39 +1941,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2100,8 +2112,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -2140,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2164,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>39.9</v>
+        <v>40.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,7 +2198,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2188,10 +2208,10 @@
         <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S7" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
         <v>78</v>
@@ -2201,39 +2221,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2376,8 +2392,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -2416,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2440,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>38.3</v>
+        <v>39.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,7 +2478,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2464,10 +2488,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
@@ -2477,39 +2501,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -2652,8 +2672,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -2667,12 +2695,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2692,12 +2720,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2716,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>36.6</v>
+        <v>37.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,62 +2758,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>37</v>
+        <v>13.2</v>
       </c>
       <c r="Q9" t="n">
         <v>21.5</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>44.1</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2805,27 +2829,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2835,67 +2859,67 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>86.48</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.3924</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1692</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1471</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2928,8 +2952,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -2943,24 +2975,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -2968,22 +3000,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2992,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>36.2</v>
+        <v>37.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,65 +3038,61 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>25.8</v>
+        <v>37</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.6</v>
+        <v>21.5</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S10" t="n">
-        <v>95.5</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>23.4</v>
+        <v>44.1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -3081,27 +3109,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3111,101 +3139,109 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>86.48</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>100.3924</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1692</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1471</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -3219,24 +3255,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -3244,22 +3280,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3268,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36</v>
+        <v>37.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,65 +3318,61 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>13.2</v>
+        <v>25.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>21.5</v>
+        <v>9.6</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S11" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>77.40000000000001</v>
+        <v>23.4</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3357,27 +3389,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3387,101 +3419,109 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -3495,24 +3535,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -3520,22 +3560,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3544,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34.9</v>
+        <v>36.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,65 +3598,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>36.3</v>
+        <v>49.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.699999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3633,12 +3669,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3648,12 +3684,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 1/25, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3663,101 +3699,109 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>101.7218</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>76.72</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>70.86</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -3771,12 +3815,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3796,12 +3840,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3820,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>33</v>
+        <v>35.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,62 +3878,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>32.4</v>
+        <v>36.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>10.1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3909,27 +3949,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3939,67 +3979,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -4032,8 +4072,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -4052,7 +4100,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Angel Martínez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4072,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4096,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.6</v>
+        <v>33.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,7 +4158,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4120,10 +4168,10 @@
         <v>9.6</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -4133,39 +4181,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4308,8 +4352,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -4348,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4372,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.6</v>
+        <v>33.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,7 +4438,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4396,10 +4448,10 @@
         <v>20.1</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -4409,39 +4461,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -4584,8 +4632,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -4599,24 +4655,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>682668</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luisangel Acuna</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -4624,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4634,12 +4690,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4648,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>27.7</v>
+        <v>27.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,65 +4718,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>21.5</v>
+        <v>9.6</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>23.4</v>
+        <v>72.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4737,27 +4789,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/13, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,101 +4819,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.32</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.2967</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3165</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0721</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2696</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0449</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -4875,12 +4935,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4900,12 +4960,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4924,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>27</v>
+        <v>27.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,65 +4998,61 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>13.7</v>
+        <v>20.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>72.7</v>
+        <v>12</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -5013,7 +5069,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
@@ -5023,17 +5079,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5043,84 +5099,84 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
+          <t>87.6</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>98.2866</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>0.347</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>0.123</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>0.299</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>69.7</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
           <t>87.3</t>
         </is>
       </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>97.253</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>0.3524</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>0.1067</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>0.2943</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>69.86</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>6.52</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>43.71</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>25.23</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>0.1287</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>34.0</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>87.3</t>
-        </is>
-      </c>
       <c r="BD17" t="inlineStr">
         <is>
           <t>0.224</t>
@@ -5136,8 +5192,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -5151,12 +5215,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5176,12 +5240,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5200,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>26.9</v>
+        <v>27.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,65 +5278,61 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>20.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>12</v>
+        <v>43.1</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5289,12 +5349,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5304,7 +5364,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -5319,67 +5379,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -5412,8 +5472,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -5427,12 +5495,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>595978</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Austin Hedges</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5452,12 +5520,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5476,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,62 +5558,58 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>12.3</v>
       </c>
       <c r="Q19" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S19" t="n">
-        <v>88.7</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>43.1</v>
+        <v>28.9</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5565,27 +5629,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5595,67 +5659,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>86.52</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.7334</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0951</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2707</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>69.82</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>47.88</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1258</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -5688,8 +5752,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -6054,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6078,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>56.2</v>
+        <v>57.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6174,10 @@
         <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -6115,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -6290,8 +6358,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -6330,12 +6406,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -6354,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>49.9</v>
+        <v>51.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6454,10 @@
         <v>21.5</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
@@ -6391,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6638,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -6606,12 +6686,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -6630,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>47.3</v>
+        <v>48.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6734,10 @@
         <v>21.5</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
@@ -6667,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6842,8 +6918,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -6882,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6906,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.5</v>
+        <v>46.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -6930,10 +7014,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
@@ -6943,39 +7027,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7118,8 +7198,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -7158,12 +7246,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -7182,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>42.9</v>
+        <v>41.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,7 +7284,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7206,10 +7294,10 @@
         <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
@@ -7219,39 +7307,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7394,8 +7478,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -7434,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7458,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>39.9</v>
+        <v>40.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,7 +7564,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -7482,10 +7574,10 @@
         <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S7" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
         <v>78</v>
@@ -7495,39 +7587,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7670,8 +7758,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -7710,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7734,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>38.3</v>
+        <v>39.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,7 +7844,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7758,10 +7854,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
@@ -7771,39 +7867,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -7946,8 +8038,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -7961,12 +8061,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7986,12 +8086,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8010,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>36.6</v>
+        <v>37.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,62 +8124,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>37</v>
+        <v>13.2</v>
       </c>
       <c r="Q9" t="n">
         <v>21.5</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>44.1</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8099,27 +8195,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -8129,67 +8225,67 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>86.48</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.3924</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1692</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1471</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -8222,8 +8318,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -8237,24 +8341,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -8262,22 +8366,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -8286,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>36.2</v>
+        <v>37.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,65 +8404,61 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>25.8</v>
+        <v>37</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.6</v>
+        <v>21.5</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S10" t="n">
-        <v>95.5</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>23.4</v>
+        <v>44.1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -8375,27 +8475,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -8405,101 +8505,109 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>86.48</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>100.3924</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1692</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1471</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -8513,24 +8621,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -8538,22 +8646,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -8562,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36</v>
+        <v>37.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,65 +8684,61 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>13.2</v>
+        <v>25.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>21.5</v>
+        <v>9.6</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S11" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>77.40000000000001</v>
+        <v>23.4</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -8651,27 +8755,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8681,101 +8785,109 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -8789,24 +8901,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -8814,22 +8926,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -8838,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34.9</v>
+        <v>36.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,65 +8964,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>36.3</v>
+        <v>49.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.699999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -8927,12 +9035,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -8942,12 +9050,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 1/25, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -8957,101 +9065,109 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>101.7218</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>76.72</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>70.86</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -9065,12 +9181,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9090,12 +9206,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9114,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>33</v>
+        <v>35.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,62 +9244,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>32.4</v>
+        <v>36.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>10.1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9203,27 +9315,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9233,67 +9345,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -9326,8 +9438,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -9346,7 +9466,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Angel Martínez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9366,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9390,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.6</v>
+        <v>33.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,7 +9524,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9414,10 +9534,10 @@
         <v>9.6</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -9427,39 +9547,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9602,8 +9718,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -9642,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9666,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.6</v>
+        <v>33.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,7 +9804,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -9690,10 +9814,10 @@
         <v>20.1</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -9703,39 +9827,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -9878,8 +9998,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -9893,24 +10021,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>682668</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luisangel Acuna</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -9918,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -9928,12 +10056,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -9942,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>27.7</v>
+        <v>27.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,65 +10084,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>21.5</v>
+        <v>9.6</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>23.4</v>
+        <v>72.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -10031,27 +10155,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/13, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,101 +10185,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.32</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.2967</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3165</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0721</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2696</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0449</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -10169,12 +10301,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10194,12 +10326,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10218,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>27</v>
+        <v>27.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,65 +10364,61 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>13.7</v>
+        <v>20.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>72.7</v>
+        <v>12</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -10307,7 +10435,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
@@ -10317,17 +10445,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10337,84 +10465,84 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
+          <t>87.6</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>98.2866</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>0.347</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>0.123</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>0.299</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>69.7</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
           <t>87.3</t>
         </is>
       </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>97.253</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>0.3524</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>0.1067</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>0.2943</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>69.86</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>6.52</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>43.71</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>25.23</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>0.1287</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>34.0</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>87.3</t>
-        </is>
-      </c>
       <c r="BD17" t="inlineStr">
         <is>
           <t>0.224</t>
@@ -10430,8 +10558,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -10445,12 +10581,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10470,12 +10606,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10494,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>26.9</v>
+        <v>27.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,65 +10644,61 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>20.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>12</v>
+        <v>43.1</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -10583,12 +10715,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10598,7 +10730,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -10613,67 +10745,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -10706,8 +10838,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -10721,12 +10861,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>595978</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Austin Hedges</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10746,12 +10886,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -10770,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,62 +10924,58 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>12.3</v>
       </c>
       <c r="Q19" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S19" t="n">
-        <v>88.7</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>43.1</v>
+        <v>28.9</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10859,27 +10995,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -10889,67 +11025,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>86.52</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.7334</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0951</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2707</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>69.82</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>47.88</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1258</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -10982,8 +11118,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Rate Field</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,11 +784,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>66.8</v>
+        <v>70.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>54.7</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1036,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>53.2</v>
+        <v>56.9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>54.7</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1312,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>52.3</v>
+        <v>55.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>54.7</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -1373,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1548,8 +1552,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1588,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1612,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>51.9</v>
+        <v>55.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1636,10 +1648,10 @@
         <v>47</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -1649,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1824,8 +1832,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1864,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1888,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>49.9</v>
+        <v>53.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,7 +1918,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1912,10 +1928,10 @@
         <v>47</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -1925,39 +1941,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -2100,8 +2112,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2140,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2164,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>49.2</v>
+        <v>52.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,7 +2198,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2188,10 +2208,10 @@
         <v>54.7</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -2201,39 +2221,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2376,8 +2392,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2416,12 +2440,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2440,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.6</v>
+        <v>51.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,7 +2478,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2464,10 +2488,10 @@
         <v>54.7</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S8" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -2477,39 +2501,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2652,8 +2672,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2692,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2716,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>46.6</v>
+        <v>50.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2740,10 +2768,10 @@
         <v>47</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
@@ -2753,39 +2781,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2928,8 +2952,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2968,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2992,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>45.2</v>
+        <v>48.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3048,10 @@
         <v>54.7</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -3029,39 +3061,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -3204,8 +3232,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3224,7 +3260,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3244,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>44.7</v>
+        <v>48.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,7 +3318,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3292,10 +3328,10 @@
         <v>44.9</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
         <v>75</v>
@@ -3305,39 +3341,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3480,8 +3512,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3495,24 +3535,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -3520,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3530,12 +3570,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3544,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>42.3</v>
+        <v>46.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,65 +3598,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>24</v>
+        <v>32.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>53.5</v>
+        <v>44.9</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T12" t="n">
         <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>45</v>
+        <v>48.7</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3633,131 +3669,139 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>25.86</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>30.98</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3771,24 +3815,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>686668</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Brenton Doyle</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -3796,22 +3840,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3820,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>41.5</v>
+        <v>44.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,62 +3878,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>32.4</v>
+        <v>28.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>44.9</v>
+        <v>54.7</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>82</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3909,7 +3949,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -3919,121 +3959,129 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>89.34</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>99.9948</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1259</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2615</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>15.93</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1332</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>30.98</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>25.86</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4047,12 +4095,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4072,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4096,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>41.1</v>
+        <v>43.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,65 +4158,61 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>44.9</v>
+        <v>47</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>36.3</v>
+        <v>12</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -4185,7 +4229,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -4195,17 +4239,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4215,67 +4259,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -4308,8 +4352,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4348,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4372,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>39.2</v>
+        <v>42.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,7 +4438,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4396,10 +4448,10 @@
         <v>54.7</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
         <v>80</v>
@@ -4409,39 +4461,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4584,8 +4632,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4599,24 +4655,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -4624,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4634,12 +4690,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4648,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>38.5</v>
+        <v>42</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,65 +4718,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>20.9</v>
+        <v>13.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>47</v>
+        <v>54.7</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>12</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4737,131 +4789,139 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>30.98</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>25.86</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4900,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4924,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>38.1</v>
+        <v>41.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,7 +4998,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -4948,10 +5008,10 @@
         <v>47</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S17" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
@@ -4961,39 +5021,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5136,8 +5192,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -5151,24 +5215,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -5176,22 +5240,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5200,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>36.7</v>
+        <v>39.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,62 +5278,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>54.7</v>
+        <v>44.9</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>77.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5294,7 +5354,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5309,111 +5369,119 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>25.86</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>30.98</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -5427,12 +5495,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5452,12 +5520,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5476,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.5</v>
+        <v>37.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,62 +5558,58 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>13.7</v>
+        <v>7.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>44.9</v>
+        <v>47</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>72.7</v>
+        <v>38.3</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5565,27 +5629,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5595,67 +5659,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -5688,8 +5752,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6054,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6078,11 +6150,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>66.8</v>
+        <v>70.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -6092,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6174,10 @@
         <v>54.7</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -6115,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -6290,8 +6358,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6330,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6354,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>53.2</v>
+        <v>56.9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6454,10 @@
         <v>54.7</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -6391,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6638,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6606,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6630,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>52.3</v>
+        <v>55.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6734,10 @@
         <v>54.7</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -6667,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6842,8 +6918,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6882,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6906,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>51.9</v>
+        <v>55.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -6930,10 +7014,10 @@
         <v>47</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -6943,39 +7027,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7118,8 +7198,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7158,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7182,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>49.9</v>
+        <v>53.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,7 +7284,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7206,10 +7294,10 @@
         <v>47</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -7219,39 +7307,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7394,8 +7478,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7434,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7458,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>49.2</v>
+        <v>52.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,7 +7564,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -7482,10 +7574,10 @@
         <v>54.7</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -7495,39 +7587,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7670,8 +7758,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7710,12 +7806,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7734,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.6</v>
+        <v>51.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,7 +7844,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7758,10 +7854,10 @@
         <v>54.7</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S8" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -7771,39 +7867,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7946,8 +8038,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7986,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8010,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>46.6</v>
+        <v>50.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,7 +8124,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8034,10 +8134,10 @@
         <v>47</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
@@ -8047,39 +8147,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8222,8 +8318,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8262,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8286,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>45.2</v>
+        <v>48.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8414,10 @@
         <v>54.7</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -8323,39 +8427,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -8498,8 +8598,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8518,7 +8626,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8538,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>44.7</v>
+        <v>48.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,7 +8684,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8586,10 +8694,10 @@
         <v>44.9</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
         <v>75</v>
@@ -8599,39 +8707,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8774,8 +8878,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8789,24 +8901,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -8814,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8824,12 +8936,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -8838,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>42.3</v>
+        <v>46.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,65 +8964,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>24</v>
+        <v>32.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>53.5</v>
+        <v>44.9</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T12" t="n">
         <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>45</v>
+        <v>48.7</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -8927,131 +9035,139 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>25.86</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>30.98</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9065,24 +9181,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>686668</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Brenton Doyle</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -9090,22 +9206,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -9114,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>41.5</v>
+        <v>44.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,62 +9244,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>32.4</v>
+        <v>28.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>44.9</v>
+        <v>54.7</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>82</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9203,7 +9315,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -9213,121 +9325,129 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>89.34</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>99.9948</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1259</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2615</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>15.93</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1332</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>30.98</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>25.86</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9341,12 +9461,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9366,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9390,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>41.1</v>
+        <v>43.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,65 +9524,61 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>44.9</v>
+        <v>47</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>36.3</v>
+        <v>12</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -9479,7 +9595,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -9489,17 +9605,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9509,67 +9625,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -9602,8 +9718,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9642,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9666,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>39.2</v>
+        <v>42.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,7 +9804,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -9690,10 +9814,10 @@
         <v>54.7</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
         <v>80</v>
@@ -9703,39 +9827,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9878,8 +9998,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9893,24 +10021,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -9918,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -9928,12 +10056,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -9942,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>38.5</v>
+        <v>42</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,65 +10084,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>20.9</v>
+        <v>13.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>47</v>
+        <v>54.7</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>12</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -10031,131 +10155,139 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>30.98</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>25.86</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10194,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10218,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>38.1</v>
+        <v>41.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,7 +10364,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -10242,10 +10374,10 @@
         <v>47</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S17" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
@@ -10255,39 +10387,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10430,8 +10558,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10445,24 +10581,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -10470,22 +10606,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -10494,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>36.7</v>
+        <v>39.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,62 +10644,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>54.7</v>
+        <v>44.9</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>77.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10588,7 +10720,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10603,111 +10735,119 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>25.86</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>30.98</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10721,12 +10861,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10746,12 +10886,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -10770,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.5</v>
+        <v>37.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,62 +10924,58 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>13.7</v>
+        <v>7.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>44.9</v>
+        <v>47</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>72.7</v>
+        <v>38.3</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10859,27 +10995,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -10889,67 +11025,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -10982,8 +11118,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Progressive Field</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>70.5</v>
+        <v>73</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>54.7</v>
       </c>
       <c r="R2" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>56.9</v>
+        <v>59.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>54.7</v>
       </c>
       <c r="R3" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>55.9</v>
+        <v>58.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>54.7</v>
       </c>
       <c r="R4" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.6</v>
+        <v>58.1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>47</v>
       </c>
       <c r="R5" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>94.90000000000001</v>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>53.5</v>
+        <v>56.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>47</v>
       </c>
       <c r="R6" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.8</v>
+        <v>55.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>54.7</v>
       </c>
       <c r="R7" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S7" t="n">
         <v>86.40000000000001</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>51.3</v>
+        <v>53.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>54.7</v>
       </c>
       <c r="R8" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>52.4</v>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>50.2</v>
+        <v>52.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>47</v>
       </c>
       <c r="R9" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>86.40000000000001</v>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>48.9</v>
+        <v>51.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>54.7</v>
       </c>
       <c r="R10" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>93.2</v>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>48.3</v>
+        <v>50.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>44.9</v>
       </c>
       <c r="R11" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>46.8</v>
+        <v>49.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>44.9</v>
       </c>
       <c r="R12" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>64.3</v>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>44.6</v>
+        <v>47.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>54.7</v>
       </c>
       <c r="R13" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>44.8</v>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>43.8</v>
+        <v>46.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>47</v>
       </c>
       <c r="R14" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>42.9</v>
+        <v>45.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>54.7</v>
       </c>
       <c r="R15" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>76.2</v>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>42</v>
+        <v>44.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>54.7</v>
       </c>
       <c r="R16" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -4914,12 +4914,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>41.8</v>
+        <v>44.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>47</v>
       </c>
       <c r="R17" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>93.2</v>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>39.1</v>
+        <v>41.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>44.9</v>
       </c>
       <c r="R18" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>37.2</v>
+        <v>39.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>47</v>
       </c>
       <c r="R19" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>70.5</v>
+        <v>73</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>54.7</v>
       </c>
       <c r="R2" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>56.9</v>
+        <v>59.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>54.7</v>
       </c>
       <c r="R3" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>55.9</v>
+        <v>58.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>54.7</v>
       </c>
       <c r="R4" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -6920,12 +6920,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.6</v>
+        <v>58.1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>47</v>
       </c>
       <c r="R5" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>94.90000000000001</v>
@@ -7200,12 +7200,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>53.5</v>
+        <v>56.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>47</v>
       </c>
       <c r="R6" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.8</v>
+        <v>55.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>54.7</v>
       </c>
       <c r="R7" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S7" t="n">
         <v>86.40000000000001</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>51.3</v>
+        <v>53.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>54.7</v>
       </c>
       <c r="R8" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>52.4</v>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>50.2</v>
+        <v>52.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>47</v>
       </c>
       <c r="R9" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>86.40000000000001</v>
@@ -8320,12 +8320,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>48.9</v>
+        <v>51.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>54.7</v>
       </c>
       <c r="R10" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>93.2</v>
@@ -8600,12 +8600,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>48.3</v>
+        <v>50.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>44.9</v>
       </c>
       <c r="R11" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -8880,12 +8880,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>46.8</v>
+        <v>49.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>44.9</v>
       </c>
       <c r="R12" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>64.3</v>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>44.6</v>
+        <v>47.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>54.7</v>
       </c>
       <c r="R13" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>44.8</v>
@@ -9440,12 +9440,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>43.8</v>
+        <v>46.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>47</v>
       </c>
       <c r="R14" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>42.9</v>
+        <v>45.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>54.7</v>
       </c>
       <c r="R15" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>76.2</v>
@@ -10000,12 +10000,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>42</v>
+        <v>44.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>54.7</v>
       </c>
       <c r="R16" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>41.8</v>
+        <v>44.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>47</v>
       </c>
       <c r="R17" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>93.2</v>
@@ -10560,12 +10560,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>39.1</v>
+        <v>41.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>44.9</v>
       </c>
       <c r="R18" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -10840,12 +10840,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>37.2</v>
+        <v>39.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>47</v>
       </c>
       <c r="R19" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -11120,12 +11120,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,12 +760,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>54.8</v>
+        <v>57.4</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>18.6</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S2" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -1036,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>49.7</v>
+        <v>52</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>26.6</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -1287,24 +1295,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -1312,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1322,21 +1330,21 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>47.6</v>
+        <v>50.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,62 +1358,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>51.1</v>
+        <v>59.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>18.6</v>
+        <v>26.6</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>100</v>
+        <v>16.6</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1425,131 +1429,139 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>69.77</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>69.02</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+          <t>25.27</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -1563,24 +1575,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -1588,31 +1600,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>47</v>
+        <v>50.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,62 +1638,58 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>59.6</v>
+        <v>51.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>26.6</v>
+        <v>18.6</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S5" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>16.6</v>
+        <v>100</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1701,131 +1709,139 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>69.77</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>25.27</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -1864,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1888,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>45.4</v>
+        <v>47.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,7 +1918,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1912,10 +1928,10 @@
         <v>26.6</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
@@ -1925,39 +1941,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2100,8 +2112,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -2115,24 +2135,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>596142</t>
+          <t>571970</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gary Sanchez</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -2140,31 +2160,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>44.3</v>
+        <v>47.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,62 +2198,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>38.4</v>
+        <v>55.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>26.6</v>
+        <v>18.6</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>28.9</v>
+        <v>18</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2253,131 +2269,139 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>47.51</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.6173</t>
+          <t>101.2892</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4781</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1782</t>
+          <t>0.2366</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3297</t>
+          <t>0.3565</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.2052</t>
+          <t>0.2347</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>25.27</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -2416,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2440,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.7</v>
+        <v>46.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,7 +2478,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2464,10 +2488,10 @@
         <v>26.6</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S8" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
@@ -2477,39 +2501,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2652,8 +2672,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -2692,12 +2720,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2716,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>42.3</v>
+        <v>45.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2740,10 +2768,10 @@
         <v>18.6</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S9" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
@@ -2753,39 +2781,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2928,8 +2952,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -2948,7 +2980,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2968,12 +3000,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2992,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>39</v>
+        <v>44.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3048,10 @@
         <v>18.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
@@ -3029,39 +3061,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3204,8 +3232,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -3219,24 +3255,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -3244,31 +3280,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.7</v>
+        <v>43.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,62 +3318,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>32.7</v>
+        <v>47.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>18.6</v>
+        <v>26.6</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>29.2</v>
+        <v>13.3</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3362,126 +3394,134 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+          <t>25.27</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -3495,12 +3535,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>683734</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Andrew Vaughn</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3520,12 +3560,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3544,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>37.9</v>
+        <v>43.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,62 +3598,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>47.1</v>
+        <v>34.2</v>
       </c>
       <c r="Q12" t="n">
         <v>26.6</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S12" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3633,12 +3669,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3648,82 +3684,82 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>100.1817</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4097</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>70.53</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>12.73</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -3756,8 +3792,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -3771,12 +3815,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3796,12 +3840,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3820,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>37.6</v>
+        <v>40.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,62 +3878,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>33.9</v>
+        <v>32.7</v>
       </c>
       <c r="Q13" t="n">
         <v>18.6</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>93.2</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>29.2</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3914,22 +3954,22 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3939,67 +3979,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -4032,8 +4072,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -4047,12 +4095,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4072,12 +4120,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4096,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>37.4</v>
+        <v>39.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,62 +4158,58 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>35.1</v>
+        <v>36.4</v>
       </c>
       <c r="Q14" t="n">
         <v>18.6</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S14" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T14" t="n">
         <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>26.1</v>
+        <v>66</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4185,22 +4229,22 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -4215,89 +4259,89 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>100.9708</t>
+          <t>99.6965</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3621</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>0.3349</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>72.85</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>38.53</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>24.2</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>0.1925</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
           <t>0.2817</t>
         </is>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>42.11</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>43.52</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>22.51</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>0.1594</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>4.89</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>34.56</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>87.74</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>0.2817</t>
-        </is>
-      </c>
       <c r="BE14" t="inlineStr">
         <is>
           <t>0.0996</t>
@@ -4308,8 +4352,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -4323,12 +4375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4348,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4372,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>35.1</v>
+        <v>36.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,62 +4438,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>36.4</v>
+        <v>33.9</v>
       </c>
       <c r="Q15" t="n">
         <v>18.6</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4461,27 +4509,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4491,67 +4539,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99.6965</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -4584,8 +4632,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -4599,24 +4655,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>571771</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Enrique Hernández</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -4624,31 +4680,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.7</v>
+        <v>33.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,65 +4718,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>16.6</v>
+        <v>32.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>25</v>
+        <v>18.6</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S16" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>5.1</v>
+        <v>28.5</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4737,27 +4789,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 3/16, 1 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,101 +4819,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>39.49</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>99.9102</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3751</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.1548</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2814</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>70.82</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.1735</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>25.27</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -4900,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4924,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>30.6</v>
+        <v>33</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,7 +4998,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -4948,10 +5008,10 @@
         <v>26.6</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>78</v>
@@ -4961,39 +5021,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -5136,8 +5192,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -5151,24 +5215,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -5176,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5186,21 +5250,21 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>30.4</v>
+        <v>32.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,62 +5278,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>20.2</v>
+        <v>17.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>17.3</v>
+        <v>26.6</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U18" t="n">
-        <v>60.7</v>
+        <v>22.4</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5294,22 +5354,22 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5319,101 +5379,109 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>36.16</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.91</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.7457</t>
+          <t>99.2209</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3662</t>
+          <t>0.3403</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3084</t>
+          <t>0.2904</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1437</t>
+          <t>0.1185</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>25.27</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -5427,12 +5495,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5452,12 +5520,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5476,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.9</v>
+        <v>31.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,65 +5558,61 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>26.6</v>
+        <v>25</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>5.1</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -5565,7 +5629,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
@@ -5580,12 +5644,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5595,67 +5659,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -5688,8 +5752,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -6054,12 +6126,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6078,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>54.8</v>
+        <v>57.4</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6174,10 @@
         <v>18.6</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S2" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -6115,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6290,8 +6358,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -6330,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6354,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>49.7</v>
+        <v>52</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6454,10 @@
         <v>26.6</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
@@ -6391,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6638,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -6581,24 +6661,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -6606,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6616,21 +6696,21 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>47.6</v>
+        <v>50.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,62 +6724,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>51.1</v>
+        <v>59.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>18.6</v>
+        <v>26.6</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>100</v>
+        <v>16.6</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6719,131 +6795,139 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>69.77</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>69.02</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+          <t>25.27</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -6857,24 +6941,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -6882,31 +6966,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>47</v>
+        <v>50.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,62 +7004,58 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>59.6</v>
+        <v>51.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>26.6</v>
+        <v>18.6</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S5" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>16.6</v>
+        <v>100</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6995,131 +7075,139 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>69.77</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>25.27</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -7158,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7182,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>45.4</v>
+        <v>47.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,7 +7284,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7206,10 +7294,10 @@
         <v>26.6</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
@@ -7219,39 +7307,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7394,8 +7478,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -7409,24 +7501,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>596142</t>
+          <t>571970</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gary Sanchez</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -7434,31 +7526,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>44.3</v>
+        <v>47.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,62 +7564,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>38.4</v>
+        <v>55.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>26.6</v>
+        <v>18.6</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>28.9</v>
+        <v>18</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7547,131 +7635,139 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>47.51</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.6173</t>
+          <t>101.2892</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4781</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1782</t>
+          <t>0.2366</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3297</t>
+          <t>0.3565</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.2052</t>
+          <t>0.2347</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>25.27</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -7710,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7734,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.7</v>
+        <v>46.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,7 +7844,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7758,10 +7854,10 @@
         <v>26.6</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S8" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
@@ -7771,39 +7867,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7946,8 +8038,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -7986,12 +8086,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8010,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>42.3</v>
+        <v>45.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,7 +8124,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8034,10 +8134,10 @@
         <v>18.6</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S9" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
@@ -8047,39 +8147,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8222,8 +8318,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -8242,7 +8346,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8262,12 +8366,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8286,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>39</v>
+        <v>44.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8414,10 @@
         <v>18.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
@@ -8323,39 +8427,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8498,8 +8598,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -8513,24 +8621,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -8538,31 +8646,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.7</v>
+        <v>43.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,62 +8684,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>32.7</v>
+        <v>47.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>18.6</v>
+        <v>26.6</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>29.2</v>
+        <v>13.3</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8656,126 +8760,134 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+          <t>25.27</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -8789,12 +8901,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>683734</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Andrew Vaughn</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -8814,12 +8926,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -8838,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>37.9</v>
+        <v>43.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,62 +8964,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>47.1</v>
+        <v>34.2</v>
       </c>
       <c r="Q12" t="n">
         <v>26.6</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S12" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8927,12 +9035,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -8942,82 +9050,82 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>100.1817</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4097</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>70.53</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>12.73</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -9050,8 +9158,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -9065,12 +9181,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9090,12 +9206,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9114,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>37.6</v>
+        <v>40.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,62 +9244,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>33.9</v>
+        <v>32.7</v>
       </c>
       <c r="Q13" t="n">
         <v>18.6</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>93.2</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>29.2</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9208,22 +9320,22 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9233,67 +9345,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -9326,8 +9438,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -9341,12 +9461,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9366,12 +9486,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9390,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>37.4</v>
+        <v>39.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,62 +9524,58 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>35.1</v>
+        <v>36.4</v>
       </c>
       <c r="Q14" t="n">
         <v>18.6</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S14" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T14" t="n">
         <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>26.1</v>
+        <v>66</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9479,22 +9595,22 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -9509,89 +9625,89 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>100.9708</t>
+          <t>99.6965</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3621</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>0.3349</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>72.85</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>38.53</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>24.2</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>0.1925</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
           <t>0.2817</t>
         </is>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>42.11</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>43.52</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>22.51</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>0.1594</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>4.89</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>34.56</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>87.74</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>0.2817</t>
-        </is>
-      </c>
       <c r="BE14" t="inlineStr">
         <is>
           <t>0.0996</t>
@@ -9602,8 +9718,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -9617,12 +9741,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9642,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9666,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>35.1</v>
+        <v>36.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,62 +9804,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>36.4</v>
+        <v>33.9</v>
       </c>
       <c r="Q15" t="n">
         <v>18.6</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9755,27 +9875,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9785,67 +9905,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99.6965</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -9878,8 +9998,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -9893,24 +10021,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>571771</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Enrique Hernández</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -9918,31 +10046,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.7</v>
+        <v>33.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,65 +10084,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>16.6</v>
+        <v>32.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>25</v>
+        <v>18.6</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S16" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>5.1</v>
+        <v>28.5</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -10031,27 +10155,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 3/16, 1 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,101 +10185,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>39.49</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>99.9102</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3751</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.1548</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2814</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>70.82</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.1735</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>25.27</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -10194,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10218,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>30.6</v>
+        <v>33</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,7 +10364,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -10242,10 +10374,10 @@
         <v>26.6</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>78</v>
@@ -10255,39 +10387,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -10430,8 +10558,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -10445,24 +10581,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -10470,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10480,21 +10616,21 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>30.4</v>
+        <v>32.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,62 +10644,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>20.2</v>
+        <v>17.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>17.3</v>
+        <v>26.6</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U18" t="n">
-        <v>60.7</v>
+        <v>22.4</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10588,22 +10720,22 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10613,101 +10745,109 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>36.16</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.91</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.7457</t>
+          <t>99.2209</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3662</t>
+          <t>0.3403</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3084</t>
+          <t>0.2904</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1437</t>
+          <t>0.1185</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>25.27</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -10721,12 +10861,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10746,12 +10886,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -10770,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.9</v>
+        <v>31.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,65 +10924,61 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>26.6</v>
+        <v>25</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>39.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>5.1</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -10859,7 +10995,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
@@ -10874,12 +11010,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -10889,67 +11025,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -10982,8 +11118,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>American Family Field</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>57.4</v>
+        <v>57.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>18.6</v>
       </c>
       <c r="R2" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>26.6</v>
       </c>
       <c r="R3" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S3" t="n">
         <v>93.2</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.5</v>
+        <v>50.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>26.6</v>
       </c>
       <c r="R4" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S4" t="n">
         <v>94.90000000000001</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>18.6</v>
       </c>
       <c r="R5" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S5" t="n">
         <v>96.59999999999999</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47.7</v>
+        <v>47.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>26.6</v>
       </c>
       <c r="R6" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>18.6</v>
       </c>
       <c r="R7" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S7" t="n">
         <v>76.2</v>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.1</v>
+        <v>46.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>26.6</v>
       </c>
       <c r="R8" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>18.6</v>
       </c>
       <c r="R9" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.4</v>
+        <v>44.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>18.6</v>
       </c>
       <c r="R10" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S10" t="n">
         <v>86.40000000000001</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.6</v>
+        <v>43.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>26.6</v>
       </c>
       <c r="R11" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>43.3</v>
+        <v>43.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>26.6</v>
       </c>
       <c r="R12" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S12" t="n">
         <v>86.40000000000001</v>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>18.6</v>
       </c>
       <c r="R13" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S13" t="n">
         <v>93.2</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>18.6</v>
       </c>
       <c r="R14" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S14" t="n">
         <v>64.3</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>18.6</v>
       </c>
       <c r="R15" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
         <v>52.4</v>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>18.6</v>
       </c>
       <c r="R16" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S16" t="n">
         <v>44.8</v>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>26.6</v>
       </c>
       <c r="R17" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S17" t="n">
         <v>64.3</v>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>32.3</v>
+        <v>32.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>26.6</v>
       </c>
       <c r="R18" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>25</v>
       </c>
       <c r="R19" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>57.4</v>
+        <v>57.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>18.6</v>
       </c>
       <c r="R2" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>26.6</v>
       </c>
       <c r="R3" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S3" t="n">
         <v>93.2</v>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.5</v>
+        <v>50.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>26.6</v>
       </c>
       <c r="R4" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S4" t="n">
         <v>94.90000000000001</v>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>18.6</v>
       </c>
       <c r="R5" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S5" t="n">
         <v>96.59999999999999</v>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47.7</v>
+        <v>47.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>26.6</v>
       </c>
       <c r="R6" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>18.6</v>
       </c>
       <c r="R7" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S7" t="n">
         <v>76.2</v>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.1</v>
+        <v>46.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>26.6</v>
       </c>
       <c r="R8" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>18.6</v>
       </c>
       <c r="R9" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.4</v>
+        <v>44.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>18.6</v>
       </c>
       <c r="R10" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S10" t="n">
         <v>86.40000000000001</v>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.6</v>
+        <v>43.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>26.6</v>
       </c>
       <c r="R11" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>43.3</v>
+        <v>43.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>26.6</v>
       </c>
       <c r="R12" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S12" t="n">
         <v>86.40000000000001</v>
@@ -9160,7 +9160,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>18.6</v>
       </c>
       <c r="R13" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S13" t="n">
         <v>93.2</v>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>18.6</v>
       </c>
       <c r="R14" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S14" t="n">
         <v>64.3</v>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>18.6</v>
       </c>
       <c r="R15" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
         <v>52.4</v>
@@ -10000,7 +10000,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>18.6</v>
       </c>
       <c r="R16" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S16" t="n">
         <v>44.8</v>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>26.6</v>
       </c>
       <c r="R17" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S17" t="n">
         <v>64.3</v>
@@ -10560,7 +10560,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>32.3</v>
+        <v>32.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>26.6</v>
       </c>
       <c r="R18" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -10840,7 +10840,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>25</v>
       </c>
       <c r="R19" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -11120,7 +11120,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -826,7 +826,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -2667,24 +2667,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -2697,26 +2697,26 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>42.4</v>
+        <v>41.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,26 +2730,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>43.6</v>
+        <v>25.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.5</v>
+        <v>31.6</v>
       </c>
       <c r="R9" t="n">
         <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U9" t="n">
-        <v>54.9</v>
+        <v>23.4</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2758,12 +2758,12 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2810,22 +2810,22 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2835,97 +2835,97 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr"/>
@@ -2943,12 +2943,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>41.5</v>
+        <v>38.3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,11 +3006,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>25.8</v>
+        <v>32.4</v>
       </c>
       <c r="Q10" t="n">
         <v>31.6</v>
@@ -3019,13 +3019,13 @@
         <v>27.6</v>
       </c>
       <c r="S10" t="n">
-        <v>95.5</v>
+        <v>47.9</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
       </c>
       <c r="U10" t="n">
-        <v>23.4</v>
+        <v>48.7</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3034,12 +3034,12 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3081,22 +3081,22 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -3111,67 +3111,67 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Angel Martinez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>40</v>
+        <v>37.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>32.4</v>
+        <v>22.9</v>
       </c>
       <c r="Q11" t="n">
         <v>31.6</v>
@@ -3295,13 +3295,13 @@
         <v>27.6</v>
       </c>
       <c r="S11" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T11" t="n">
         <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>48.7</v>
+        <v>36.3</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3310,12 +3310,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -3357,22 +3357,22 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -3387,67 +3387,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>98.404</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2858</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>36.9</v>
+        <v>35.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -3586,12 +3586,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>33.4</v>
+        <v>34.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T14" t="n">
         <v>78</v>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -4599,24 +4599,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -4634,21 +4634,21 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.3</v>
+        <v>30.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4666,10 +4666,10 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.1</v>
+        <v>23.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>33.4</v>
+        <v>21.5</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
@@ -4678,10 +4678,10 @@
         <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>0.8</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,97 +4767,97 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>98.4476</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1223</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2522</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1044</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr"/>
@@ -4875,12 +4875,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>810938</t>
+          <t>663743</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>28.5</v>
+        <v>29.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>11.6</v>
+        <v>12.8</v>
       </c>
       <c r="Q17" t="n">
         <v>21.5</v>
@@ -4957,7 +4957,7 @@
         <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -5018,17 +5018,17 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5043,67 +5043,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.03</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>98.4446</t>
+          <t>99.0812</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.3248</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0789</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2809</t>
+          <t>0.2721</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>72.49</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.0731</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>27.1</v>
+        <v>24.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,11 +5214,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" t="n">
         <v>21.5</v>
@@ -5227,13 +5227,13 @@
         <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T18" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>15.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -5242,12 +5242,12 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5289,27 +5289,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5319,67 +5319,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5476,7 +5476,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>25.6</v>
+        <v>24.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>27.6</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -5518,12 +5518,12 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -7961,24 +7961,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -7991,26 +7991,26 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>42.4</v>
+        <v>41.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,26 +8024,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>43.6</v>
+        <v>25.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.5</v>
+        <v>31.6</v>
       </c>
       <c r="R9" t="n">
         <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U9" t="n">
-        <v>54.9</v>
+        <v>23.4</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -8104,22 +8104,22 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -8129,97 +8129,97 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr"/>
@@ -8237,12 +8237,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8286,7 +8286,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>41.5</v>
+        <v>38.3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,11 +8300,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>25.8</v>
+        <v>32.4</v>
       </c>
       <c r="Q10" t="n">
         <v>31.6</v>
@@ -8313,13 +8313,13 @@
         <v>27.6</v>
       </c>
       <c r="S10" t="n">
-        <v>95.5</v>
+        <v>47.9</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
       </c>
       <c r="U10" t="n">
-        <v>23.4</v>
+        <v>48.7</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -8328,12 +8328,12 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -8375,22 +8375,22 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -8405,67 +8405,67 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Angel Martinez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8562,7 +8562,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>40</v>
+        <v>37.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>32.4</v>
+        <v>22.9</v>
       </c>
       <c r="Q11" t="n">
         <v>31.6</v>
@@ -8589,13 +8589,13 @@
         <v>27.6</v>
       </c>
       <c r="S11" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T11" t="n">
         <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>48.7</v>
+        <v>36.3</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -8604,12 +8604,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -8651,22 +8651,22 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -8681,67 +8681,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>98.404</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2858</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -8819,7 +8819,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>36.9</v>
+        <v>35.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -8880,12 +8880,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9390,7 +9390,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>33.4</v>
+        <v>34.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T14" t="n">
         <v>78</v>
@@ -9432,12 +9432,12 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -9893,24 +9893,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -9928,21 +9928,21 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.3</v>
+        <v>30.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9960,10 +9960,10 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.1</v>
+        <v>23.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>33.4</v>
+        <v>21.5</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
@@ -9972,10 +9972,10 @@
         <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>0.8</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,97 +10061,97 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>98.4476</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1223</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2522</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1044</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr"/>
@@ -10169,12 +10169,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>810938</t>
+          <t>663743</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>28.5</v>
+        <v>29.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>11.6</v>
+        <v>12.8</v>
       </c>
       <c r="Q17" t="n">
         <v>21.5</v>
@@ -10251,7 +10251,7 @@
         <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -10312,17 +10312,17 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -10337,67 +10337,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.03</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>98.4446</t>
+          <t>99.0812</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.3248</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0789</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2809</t>
+          <t>0.2721</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>72.49</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.0731</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -10445,12 +10445,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10494,7 +10494,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>27.1</v>
+        <v>24.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,11 +10508,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" t="n">
         <v>21.5</v>
@@ -10521,13 +10521,13 @@
         <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T18" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>15.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -10536,12 +10536,12 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -10583,27 +10583,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10613,67 +10613,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -10770,7 +10770,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>25.6</v>
+        <v>24.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>27.6</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.6</v>
+        <v>54.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1036,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>48.7</v>
+        <v>51.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>33.4</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1312,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>46.6</v>
+        <v>49.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>33.4</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -1373,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1548,8 +1552,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1588,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1612,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>44.7</v>
+        <v>47.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1636,10 +1648,10 @@
         <v>21.5</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -1649,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1824,8 +1832,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1839,24 +1855,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -1864,31 +1880,31 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>43.3</v>
+        <v>46.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,62 +1918,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.4</v>
+        <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>10.1</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1977,27 +1989,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2007,101 +2019,109 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2115,24 +2135,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -2140,31 +2160,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.3</v>
+        <v>46</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,62 +2198,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>21.5</v>
+        <v>33.4</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2253,12 +2269,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2268,12 +2284,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2283,101 +2299,109 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2391,12 +2415,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2416,12 +2440,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2440,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.3</v>
+        <v>46</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,62 +2478,58 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
         <v>21.5</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>78</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2529,12 +2549,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2544,7 +2564,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2559,67 +2579,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2652,8 +2672,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2672,7 +2700,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2692,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2716,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.5</v>
+        <v>44.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2740,10 +2768,10 @@
         <v>31.6</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -2753,39 +2781,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2928,8 +2952,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2943,12 +2975,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2968,12 +3000,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2992,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>38.3</v>
+        <v>39.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,65 +3038,61 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>32.4</v>
+        <v>20.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>31.6</v>
+        <v>33.4</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>48.7</v>
+        <v>12</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -3081,27 +3109,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3111,67 +3139,67 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -3204,8 +3232,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3219,12 +3255,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3244,12 +3280,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3268,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>37.9</v>
+        <v>37.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,62 +3318,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>22.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>31.6</v>
+        <v>33.4</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>36.3</v>
+        <v>43.1</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3357,27 +3389,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3387,67 +3419,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -3480,8 +3512,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3495,24 +3535,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -3520,31 +3560,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>35.2</v>
+        <v>37.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,65 +3598,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>20.9</v>
+        <v>10.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>33.4</v>
+        <v>21.5</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>12</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3633,27 +3669,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3663,101 +3699,109 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3771,12 +3815,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3796,12 +3840,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3834,62 +3878,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.9</v>
+        <v>13.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>33.4</v>
+        <v>31.6</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S13" t="n">
-        <v>88.7</v>
+        <v>44.8</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U13" t="n">
-        <v>43.1</v>
+        <v>72.7</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3909,27 +3949,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3939,67 +3979,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -4032,8 +4072,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4047,24 +4095,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -4072,31 +4120,31 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>34.8</v>
+        <v>34.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,62 +4158,58 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>10.6</v>
+        <v>7.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>21.5</v>
+        <v>33.4</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S14" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>70.59999999999999</v>
+        <v>38.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4185,27 +4229,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4215,101 +4259,109 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4323,12 +4375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>595978</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Austin Hedges</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4348,12 +4400,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -4372,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.3</v>
+        <v>31.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,62 +4438,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>13.7</v>
+        <v>12.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>31.6</v>
+        <v>33.4</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>72.7</v>
+        <v>28.9</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4461,27 +4509,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4491,67 +4539,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.52</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>97.7334</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0951</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2707</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>69.82</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>47.88</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.1258</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -4584,8 +4632,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4599,12 +4655,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4624,12 +4680,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4648,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.7</v>
+        <v>31.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,62 +4718,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>23.3</v>
+        <v>11.6</v>
       </c>
       <c r="Q16" t="n">
         <v>21.5</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
         <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4742,7 +4794,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4752,7 +4804,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -4767,67 +4819,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -4860,8 +4912,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4875,12 +4935,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4900,12 +4960,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4924,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.8</v>
+        <v>27.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,62 +4998,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>12.8</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
         <v>21.5</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>76.2</v>
       </c>
       <c r="T17" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>18.3</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5013,27 +5069,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5043,67 +5099,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -5136,8 +5192,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5151,12 +5215,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5176,12 +5240,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5200,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>24.7</v>
+        <v>27.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,62 +5278,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>27</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5294,7 +5354,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5304,12 +5364,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5319,67 +5379,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.35</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -5412,8 +5472,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5427,12 +5495,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5452,12 +5520,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5476,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>24.6</v>
+        <v>26.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,62 +5558,58 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>27</v>
+        <v>19.5</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5570,7 +5634,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -5580,12 +5644,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5595,67 +5659,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>68.35</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0829</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -5688,8 +5752,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6054,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6078,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.6</v>
+        <v>54.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6174,10 @@
         <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -6115,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6290,8 +6358,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6330,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6354,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>48.7</v>
+        <v>51.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6454,10 @@
         <v>33.4</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -6391,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6638,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6606,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6630,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>46.6</v>
+        <v>49.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6734,10 @@
         <v>33.4</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -6667,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -6842,8 +6918,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6882,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6906,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>44.7</v>
+        <v>47.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -6930,10 +7014,10 @@
         <v>21.5</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -6943,39 +7027,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7118,8 +7198,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7133,24 +7221,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -7158,31 +7246,31 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>43.3</v>
+        <v>46.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,62 +7284,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.4</v>
+        <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>10.1</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7271,27 +7355,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -7301,101 +7385,109 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7409,24 +7501,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -7434,31 +7526,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.3</v>
+        <v>46</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,62 +7564,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>21.5</v>
+        <v>33.4</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7547,12 +7635,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -7562,12 +7650,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7577,101 +7665,109 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7685,12 +7781,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7710,12 +7806,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7734,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.3</v>
+        <v>46</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,62 +7844,58 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
         <v>21.5</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>78</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7823,12 +7915,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -7838,7 +7930,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -7853,67 +7945,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -7946,8 +8038,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7966,7 +8066,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7986,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8010,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.5</v>
+        <v>44.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,7 +8124,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8034,10 +8134,10 @@
         <v>31.6</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -8047,39 +8147,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8222,8 +8318,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8237,12 +8341,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8262,12 +8366,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8286,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>38.3</v>
+        <v>39.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,65 +8404,61 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>32.4</v>
+        <v>20.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>31.6</v>
+        <v>33.4</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>48.7</v>
+        <v>12</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -8375,27 +8475,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -8405,67 +8505,67 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -8498,8 +8598,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8513,12 +8621,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8538,12 +8646,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8562,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>37.9</v>
+        <v>37.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,62 +8684,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>22.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>31.6</v>
+        <v>33.4</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>36.3</v>
+        <v>43.1</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8651,27 +8755,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8681,67 +8785,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -8774,8 +8878,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8789,24 +8901,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -8814,31 +8926,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>35.2</v>
+        <v>37.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,65 +8964,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>20.9</v>
+        <v>10.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>33.4</v>
+        <v>21.5</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>12</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -8927,27 +9035,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -8957,101 +9065,109 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9065,12 +9181,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9090,12 +9206,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9128,62 +9244,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.9</v>
+        <v>13.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>33.4</v>
+        <v>31.6</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S13" t="n">
-        <v>88.7</v>
+        <v>44.8</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U13" t="n">
-        <v>43.1</v>
+        <v>72.7</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9203,27 +9315,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9233,67 +9345,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -9326,8 +9438,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9341,24 +9461,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -9366,31 +9486,31 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>34.8</v>
+        <v>34.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,62 +9524,58 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>10.6</v>
+        <v>7.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>21.5</v>
+        <v>33.4</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S14" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>70.59999999999999</v>
+        <v>38.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9479,27 +9595,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9509,101 +9625,109 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9617,12 +9741,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>595978</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Austin Hedges</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9642,12 +9766,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -9666,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.3</v>
+        <v>31.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,62 +9804,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>13.7</v>
+        <v>12.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>31.6</v>
+        <v>33.4</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>72.7</v>
+        <v>28.9</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9755,27 +9875,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9785,67 +9905,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.52</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>97.7334</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0951</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2707</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>69.82</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>47.88</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.1258</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -9878,8 +9998,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9893,12 +10021,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9918,12 +10046,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9942,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.7</v>
+        <v>31.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,62 +10084,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>23.3</v>
+        <v>11.6</v>
       </c>
       <c r="Q16" t="n">
         <v>21.5</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
         <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10036,7 +10160,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10046,7 +10170,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -10061,67 +10185,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -10154,8 +10278,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10169,12 +10301,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10194,12 +10326,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10218,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.8</v>
+        <v>27.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,62 +10364,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>12.8</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
         <v>21.5</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>76.2</v>
       </c>
       <c r="T17" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>18.3</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10307,27 +10435,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10337,67 +10465,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -10430,8 +10558,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10445,12 +10581,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10470,12 +10606,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10494,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>24.7</v>
+        <v>27.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,62 +10644,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>27</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10588,7 +10720,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10598,12 +10730,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10613,67 +10745,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.35</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -10706,8 +10838,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10721,12 +10861,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10746,12 +10886,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -10770,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>24.6</v>
+        <v>26.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,62 +10924,58 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>27</v>
+        <v>19.5</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10864,7 +11000,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -10874,12 +11010,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -10889,67 +11025,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>68.35</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0829</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -10982,8 +11118,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,12 +760,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>56</v>
+        <v>58.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel</t>
+          <t>Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>38.7</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S2" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -821,14 +821,14 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X2" t="inlineStr">
         <is>
           <t>5</t>
@@ -846,12 +846,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -996,8 +996,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -1011,12 +1019,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1036,12 +1044,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1060,7 +1068,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55</v>
+        <v>54.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,40 +1082,40 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>51.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q3" t="n">
         <v>38.7</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
       </c>
       <c r="U3" t="n">
-        <v>100</v>
+        <v>48.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1122,12 +1130,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1149,22 +1157,22 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1174,72 +1182,72 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1272,8 +1280,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -1287,12 +1303,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1312,12 +1328,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1336,7 +1352,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.8</v>
+        <v>54.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,40 +1366,40 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>45.7</v>
+        <v>51.1</v>
       </c>
       <c r="Q4" t="n">
         <v>38.7</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
       </c>
       <c r="U4" t="n">
-        <v>48.3</v>
+        <v>100</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1398,12 +1414,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1425,22 +1441,22 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1450,72 +1466,72 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1548,8 +1564,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -1563,12 +1587,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1588,12 +1612,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1612,7 +1636,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.1</v>
+        <v>50.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,40 +1650,40 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>32.7</v>
+        <v>36.4</v>
       </c>
       <c r="Q5" t="n">
         <v>38.7</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>29.2</v>
+        <v>66</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1674,12 +1698,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1701,22 +1725,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1731,67 +1755,67 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>99.6965</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1824,8 +1848,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -1839,12 +1871,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1864,12 +1896,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1888,7 +1920,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>44.9</v>
+        <v>48.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,40 +1934,40 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.3</v>
+        <v>32.7</v>
       </c>
       <c r="Q6" t="n">
         <v>38.7</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>13</v>
+        <v>29.2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1950,12 +1982,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1977,27 +2009,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2007,67 +2039,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2100,8 +2132,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -2115,12 +2155,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2140,12 +2180,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2164,7 +2204,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>44.1</v>
+        <v>48.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,40 +2218,40 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.4</v>
+        <v>39.3</v>
       </c>
       <c r="Q7" t="n">
         <v>38.7</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S7" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2226,12 +2266,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -2258,22 +2298,22 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2283,67 +2323,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>99.6965</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -2376,8 +2416,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -2416,7 +2464,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2440,7 +2488,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.5</v>
+        <v>46.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2464,7 +2512,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S8" t="n">
         <v>88.7</v>
@@ -2652,8 +2700,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -2667,24 +2723,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -2692,22 +2748,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2716,7 +2772,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>40.8</v>
+        <v>46.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,40 +2786,40 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>59.6</v>
+        <v>33.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>38.7</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>16.6</v>
+        <v>12</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2778,12 +2834,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -2805,12 +2861,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2820,12 +2876,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2835,101 +2891,109 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.2559</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.0609</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>22.73</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -2943,24 +3007,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -2968,22 +3032,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2992,7 +3056,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>39.8</v>
+        <v>43.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,26 +3070,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>33.9</v>
+        <v>59.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>38.7</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S10" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>12</v>
+        <v>16.6</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3039,7 +3103,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3081,12 +3145,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3096,12 +3160,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3111,101 +3175,109 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>69.02</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>83.89</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.2559</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.0609</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+          <t>22.73</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -3244,7 +3316,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3340,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>39.2</v>
+        <v>42.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3292,7 +3364,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S11" t="n">
         <v>92.09999999999999</v>
@@ -3480,8 +3552,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -3520,7 +3600,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3544,7 +3624,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38.2</v>
+        <v>41.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3568,7 +3648,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S12" t="n">
         <v>90.40000000000001</v>
@@ -3756,8 +3836,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -3796,7 +3884,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3820,7 +3908,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>37.6</v>
+        <v>40.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3844,7 +3932,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S13" t="n">
         <v>95.5</v>
@@ -4032,8 +4120,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -4072,7 +4168,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4096,7 +4192,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.2</v>
+        <v>38.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,7 +4206,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4120,10 +4216,10 @@
         <v>37.5</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -4133,14 +4229,14 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X14" t="inlineStr">
         <is>
           <t>9</t>
@@ -4158,12 +4254,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -4308,8 +4404,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -4348,7 +4452,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4372,7 +4476,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>33.6</v>
+        <v>37.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,7 +4490,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4396,10 +4500,10 @@
         <v>38.7</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
         <v>78</v>
@@ -4409,14 +4513,14 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X15" t="inlineStr">
         <is>
           <t>8</t>
@@ -4434,12 +4538,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -4584,8 +4688,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -4624,7 +4736,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4648,7 +4760,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.8</v>
+        <v>34.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4672,7 +4784,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S16" t="n">
         <v>47.9</v>
@@ -4860,8 +4972,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -4900,7 +5020,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4924,7 +5044,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>26.9</v>
+        <v>30</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4948,7 +5068,7 @@
         <v>0.9</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S17" t="n">
         <v>71.7</v>
@@ -5136,8 +5256,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -5176,7 +5304,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5200,7 +5328,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>24.5</v>
+        <v>27.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5224,7 +5352,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S18" t="n">
         <v>59.8</v>
@@ -5412,8 +5540,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -5452,7 +5588,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5476,7 +5612,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>23.8</v>
+        <v>26.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5500,7 +5636,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S19" t="n">
         <v>40.2</v>
@@ -5688,8 +5824,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -6054,12 +6198,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6078,7 +6222,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>56</v>
+        <v>58.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6236,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel</t>
+          <t>Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6246,10 @@
         <v>38.7</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S2" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -6115,14 +6259,14 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X2" t="inlineStr">
         <is>
           <t>5</t>
@@ -6140,12 +6284,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -6290,8 +6434,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -6305,12 +6457,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -6330,12 +6482,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -6354,7 +6506,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55</v>
+        <v>54.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,40 +6520,40 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>51.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q3" t="n">
         <v>38.7</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
       </c>
       <c r="U3" t="n">
-        <v>100</v>
+        <v>48.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -6416,12 +6568,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -6443,22 +6595,22 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -6468,72 +6620,72 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -6566,8 +6718,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -6581,12 +6741,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6606,12 +6766,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -6630,7 +6790,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.8</v>
+        <v>54.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,40 +6804,40 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>45.7</v>
+        <v>51.1</v>
       </c>
       <c r="Q4" t="n">
         <v>38.7</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
       </c>
       <c r="U4" t="n">
-        <v>48.3</v>
+        <v>100</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -6692,12 +6852,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -6719,22 +6879,22 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -6744,72 +6904,72 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -6842,8 +7002,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -6857,12 +7025,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6882,12 +7050,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -6906,7 +7074,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.1</v>
+        <v>50.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,40 +7088,40 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>32.7</v>
+        <v>36.4</v>
       </c>
       <c r="Q5" t="n">
         <v>38.7</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>29.2</v>
+        <v>66</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -6968,12 +7136,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -6995,22 +7163,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -7025,67 +7193,67 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>99.6965</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -7118,8 +7286,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -7133,12 +7309,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7158,12 +7334,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -7182,7 +7358,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>44.9</v>
+        <v>48.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,40 +7372,40 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.3</v>
+        <v>32.7</v>
       </c>
       <c r="Q6" t="n">
         <v>38.7</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>13</v>
+        <v>29.2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -7244,12 +7420,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -7271,27 +7447,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -7301,67 +7477,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -7394,8 +7570,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -7409,12 +7593,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7434,12 +7618,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -7458,7 +7642,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>44.1</v>
+        <v>48.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,40 +7656,40 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.4</v>
+        <v>39.3</v>
       </c>
       <c r="Q7" t="n">
         <v>38.7</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S7" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -7520,12 +7704,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -7552,22 +7736,22 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7577,67 +7761,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>99.6965</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -7670,8 +7854,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -7710,7 +7902,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7734,7 +7926,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.5</v>
+        <v>46.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7758,7 +7950,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S8" t="n">
         <v>88.7</v>
@@ -7946,8 +8138,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -7961,24 +8161,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -7986,22 +8186,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8010,7 +8210,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>40.8</v>
+        <v>46.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,40 +8224,40 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>59.6</v>
+        <v>33.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>38.7</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>16.6</v>
+        <v>12</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -8072,12 +8272,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -8099,12 +8299,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -8114,12 +8314,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -8129,101 +8329,109 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.2559</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.0609</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>22.73</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -8237,24 +8445,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -8262,22 +8470,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -8286,7 +8494,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>39.8</v>
+        <v>43.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,26 +8508,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>33.9</v>
+        <v>59.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>38.7</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S10" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>12</v>
+        <v>16.6</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -8333,7 +8541,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -8375,12 +8583,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -8390,12 +8598,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -8405,101 +8613,109 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>69.02</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>83.89</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.2559</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.0609</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+          <t>22.73</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -8538,7 +8754,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8778,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>39.2</v>
+        <v>42.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8586,7 +8802,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S11" t="n">
         <v>92.09999999999999</v>
@@ -8774,8 +8990,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -8814,7 +9038,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8838,7 +9062,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38.2</v>
+        <v>41.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8862,7 +9086,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S12" t="n">
         <v>90.40000000000001</v>
@@ -9050,8 +9274,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -9090,7 +9322,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9114,7 +9346,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>37.6</v>
+        <v>40.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9138,7 +9370,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S13" t="n">
         <v>95.5</v>
@@ -9326,8 +9558,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -9366,7 +9606,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9390,7 +9630,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.2</v>
+        <v>38.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,7 +9644,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9414,10 +9654,10 @@
         <v>37.5</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -9427,14 +9667,14 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X14" t="inlineStr">
         <is>
           <t>9</t>
@@ -9452,12 +9692,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -9602,8 +9842,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -9642,7 +9890,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9666,7 +9914,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>33.6</v>
+        <v>37.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,7 +9928,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -9690,10 +9938,10 @@
         <v>38.7</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
         <v>78</v>
@@ -9703,14 +9951,14 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X15" t="inlineStr">
         <is>
           <t>8</t>
@@ -9728,12 +9976,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -9878,8 +10126,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -9918,7 +10174,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -9942,7 +10198,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.8</v>
+        <v>34.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9966,7 +10222,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S16" t="n">
         <v>47.9</v>
@@ -10154,8 +10410,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -10194,7 +10458,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10218,7 +10482,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>26.9</v>
+        <v>30</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10242,7 +10506,7 @@
         <v>0.9</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S17" t="n">
         <v>71.7</v>
@@ -10430,8 +10694,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -10470,7 +10742,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10494,7 +10766,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>24.5</v>
+        <v>27.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10518,7 +10790,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S18" t="n">
         <v>59.8</v>
@@ -10706,8 +10978,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -10746,7 +11026,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10770,7 +11050,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>23.8</v>
+        <v>26.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10794,7 +11074,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S19" t="n">
         <v>40.2</v>
@@ -10982,8 +11262,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -826,34 +826,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1110,34 +1106,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1394,34 +1386,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1678,34 +1666,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1962,34 +1946,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2246,34 +2226,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2488,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.6</v>
+        <v>47.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2502,7 +2478,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2515,7 +2491,7 @@
         <v>48.1</v>
       </c>
       <c r="S8" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>78</v>
@@ -2525,39 +2501,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2814,34 +2786,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3056,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43.9</v>
+        <v>44.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3070,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3083,7 +3051,7 @@
         <v>48.1</v>
       </c>
       <c r="S10" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
@@ -3093,39 +3061,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3340,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.3</v>
+        <v>42.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3354,7 +3318,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3367,7 +3331,7 @@
         <v>48.1</v>
       </c>
       <c r="S11" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
         <v>78</v>
@@ -3377,39 +3341,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3575,12 +3535,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>596142</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gary Sanchez</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3605,7 +3565,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3624,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3638,11 +3598,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>38.4</v>
+        <v>36.6</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -3651,49 +3611,45 @@
         <v>48.1</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>28.9</v>
+        <v>65.2</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3713,27 +3669,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3743,67 +3699,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.6173</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1782</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3297</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.2052</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -3859,12 +3815,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>683734</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Andrew Vaughn</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3889,7 +3845,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3908,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>40.7</v>
+        <v>39.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3922,11 +3878,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>36.6</v>
+        <v>34.1</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -3935,49 +3891,45 @@
         <v>48.1</v>
       </c>
       <c r="S13" t="n">
-        <v>95.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>65.2</v>
+        <v>13.6</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3997,27 +3949,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -4027,67 +3979,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>100.1817</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4097</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>70.46</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -4234,34 +4186,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4427,24 +4375,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>500743</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -4457,17 +4405,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4476,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>37.3</v>
+        <v>38.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4490,26 +4438,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>17.3</v>
+        <v>47.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>38.7</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>48.1</v>
       </c>
       <c r="S15" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>14.1</v>
+        <v>13.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4518,34 +4466,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4565,12 +4509,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4580,112 +4524,112 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/14, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.0168</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3776</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1083</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3039</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>77.44</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>23.17</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1273</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>83.89</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.2559</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.0609</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -4711,24 +4655,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -4746,12 +4690,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4760,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>34.9</v>
+        <v>37.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4774,62 +4718,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>47.1</v>
+        <v>17.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>38.7</v>
       </c>
       <c r="R16" t="n">
         <v>48.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>13.3</v>
+        <v>14.1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4849,12 +4789,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4864,112 +4804,112 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>98.0168</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.3776</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1083</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3039</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>77.44</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.2559</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.0609</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
@@ -4995,12 +4935,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5025,7 +4965,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5044,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>30</v>
+        <v>28.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5058,62 +4998,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>16.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>48.1</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>5.1</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -5133,12 +5069,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5148,12 +5084,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5163,67 +5099,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -5279,12 +5215,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5309,7 +5245,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5328,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5342,11 +5278,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>17.1</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
@@ -5355,52 +5291,48 @@
         <v>48.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
         <v>78</v>
       </c>
       <c r="U18" t="n">
-        <v>24.9</v>
+        <v>22.4</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5417,12 +5349,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5432,7 +5364,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -5447,67 +5379,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>36.16</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.91</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>99.2209</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3403</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2904</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1185</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -5563,12 +5495,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5593,7 +5525,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5612,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.9</v>
+        <v>27.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5626,65 +5558,61 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R19" t="n">
         <v>48.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>5.1</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -5701,7 +5629,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
@@ -5716,12 +5644,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5731,67 +5659,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -6264,34 +6192,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6548,34 +6472,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6832,34 +6752,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7116,34 +7032,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7400,34 +7312,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7684,34 +7592,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7926,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.6</v>
+        <v>47.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7940,7 +7844,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7953,7 +7857,7 @@
         <v>48.1</v>
       </c>
       <c r="S8" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>78</v>
@@ -7963,39 +7867,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8252,34 +8152,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8494,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43.9</v>
+        <v>44.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8508,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8521,7 +8417,7 @@
         <v>48.1</v>
       </c>
       <c r="S10" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
@@ -8531,39 +8427,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8778,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.3</v>
+        <v>42.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8792,7 +8684,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8805,7 +8697,7 @@
         <v>48.1</v>
       </c>
       <c r="S11" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
         <v>78</v>
@@ -8815,39 +8707,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9013,12 +8901,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>596142</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gary Sanchez</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -9043,7 +8931,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -9062,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9076,11 +8964,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>38.4</v>
+        <v>36.6</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -9089,49 +8977,45 @@
         <v>48.1</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>28.9</v>
+        <v>65.2</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9151,27 +9035,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -9181,67 +9065,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.6173</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1782</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3297</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.2052</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -9297,12 +9181,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>683734</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Andrew Vaughn</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9327,7 +9211,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9346,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>40.7</v>
+        <v>39.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9360,11 +9244,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>36.6</v>
+        <v>34.1</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -9373,49 +9257,45 @@
         <v>48.1</v>
       </c>
       <c r="S13" t="n">
-        <v>95.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>65.2</v>
+        <v>13.6</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9435,27 +9315,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9465,67 +9345,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>100.1817</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4097</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>70.46</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -9672,34 +9552,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9865,24 +9741,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>500743</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -9895,17 +9771,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -9914,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>37.3</v>
+        <v>38.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9928,26 +9804,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>17.3</v>
+        <v>47.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>38.7</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>48.1</v>
       </c>
       <c r="S15" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>14.1</v>
+        <v>13.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -9956,34 +9832,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10003,12 +9875,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -10018,112 +9890,112 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/14, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.0168</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3776</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1083</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3039</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>77.44</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>23.17</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1273</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>83.89</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.2559</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.0609</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -10149,24 +10021,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -10184,12 +10056,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -10198,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>34.9</v>
+        <v>37.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10212,62 +10084,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>47.1</v>
+        <v>17.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>38.7</v>
       </c>
       <c r="R16" t="n">
         <v>48.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>13.3</v>
+        <v>14.1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10287,12 +10155,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10302,112 +10170,112 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>98.0168</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.3776</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1083</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3039</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>77.44</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.2559</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.0609</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
@@ -10433,12 +10301,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10463,7 +10331,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10482,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>30</v>
+        <v>28.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10496,62 +10364,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>16.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>48.1</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>5.1</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -10571,12 +10435,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -10586,12 +10450,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10601,67 +10465,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -10717,12 +10581,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10747,7 +10611,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10766,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10780,11 +10644,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>17.1</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
@@ -10793,52 +10657,48 @@
         <v>48.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
         <v>78</v>
       </c>
       <c r="U18" t="n">
-        <v>24.9</v>
+        <v>22.4</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -10855,12 +10715,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10870,7 +10730,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -10885,67 +10745,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>36.16</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.91</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>99.2209</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3403</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2904</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1185</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -11001,12 +10861,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -11031,7 +10891,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -11050,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.9</v>
+        <v>27.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -11064,65 +10924,61 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R19" t="n">
         <v>48.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>5.1</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -11139,7 +10995,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
@@ -11154,12 +11010,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -11169,67 +11025,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,12 +760,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,11 +784,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>57.4</v>
+        <v>63.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>39.5</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -996,8 +992,16 @@
           <t>29.7</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -1036,12 +1040,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1060,11 +1064,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55.4</v>
+        <v>61.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>39.5</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1272,8 +1272,16 @@
           <t>29.7</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -1312,12 +1320,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>53.3</v>
+        <v>59.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>35.6</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -1373,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1548,8 +1552,16 @@
           <t>29.06</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -1563,24 +1575,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -1588,31 +1600,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>49.6</v>
+        <v>55.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,65 +1638,61 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>45.7</v>
+        <v>50.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>39.5</v>
+        <v>35.6</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>48.3</v>
+        <v>63.3</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1701,12 +1709,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1716,12 +1724,12 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1731,101 +1739,109 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>0.3329</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>74.25</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>44.59</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>31.29</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>29.27</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.1951</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>89.53</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
           <t>0.3296</t>
         </is>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>72.62</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>26.95</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>34.92</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>28.4</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>0.1727</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0.375</t>
-        </is>
-      </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+          <t>29.06</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -1839,12 +1855,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1864,12 +1880,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1888,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>49.3</v>
+        <v>55.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,62 +1918,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>50.1</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
         <v>35.6</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>63.3</v>
+        <v>65.2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1982,22 +1994,22 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2007,67 +2019,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2100,8 +2112,16 @@
           <t>29.06</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -2115,24 +2135,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -2140,31 +2160,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>48.6</v>
+        <v>54.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,65 +2198,61 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.6</v>
+        <v>45.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>35.6</v>
+        <v>39.5</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>95.5</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>65.2</v>
+        <v>48.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -2253,27 +2269,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2283,101 +2299,109 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>29.06</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -2391,24 +2415,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -2416,31 +2440,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>47.5</v>
+        <v>52.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,65 +2478,61 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>47.1</v>
+        <v>32.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>35.6</v>
+        <v>39.5</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U8" t="n">
-        <v>13.3</v>
+        <v>29.2</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -2534,126 +2554,134 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>77.44</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>29.06</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -2667,24 +2695,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>571970</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -2692,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2702,21 +2730,21 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>47.3</v>
+        <v>52.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,65 +2758,61 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>55.1</v>
+        <v>47.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>39.5</v>
+        <v>35.6</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>18</v>
+        <v>13.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2805,12 +2829,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2820,116 +2844,124 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.2892</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4781</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2366</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3565</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>77.44</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2347</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>29.06</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -2943,24 +2975,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -2968,31 +3000,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>45.3</v>
+        <v>51.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,65 +3038,61 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>32.7</v>
+        <v>38.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>39.5</v>
+        <v>35.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>29.2</v>
+        <v>25.3</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -3081,12 +3109,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3096,12 +3124,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3111,101 +3139,109 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+          <t>29.06</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -3219,24 +3255,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -3244,31 +3280,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>45.1</v>
+        <v>51.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,65 +3318,61 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>39.5</v>
+        <v>35.6</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>13</v>
+        <v>37.8</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3362,22 +3394,22 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3387,101 +3419,109 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>36.44</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+          <t>29.06</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -3495,24 +3535,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -3520,31 +3560,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>44.8</v>
+        <v>51.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,65 +3598,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q12" t="n">
         <v>39.5</v>
       </c>
-      <c r="Q12" t="n">
-        <v>35.6</v>
-      </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>37.8</v>
+        <v>13</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3638,22 +3674,22 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3663,101 +3699,109 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>29.06</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -3796,12 +3840,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3820,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>44.3</v>
+        <v>49.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,7 +3878,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3844,10 +3888,10 @@
         <v>39.5</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T13" t="n">
         <v>78</v>
@@ -3857,39 +3901,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4032,8 +4072,16 @@
           <t>29.7</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -4047,24 +4095,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -4072,31 +4120,31 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>43.8</v>
+        <v>47.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,65 +4158,61 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>38.2</v>
+        <v>33.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>35.6</v>
+        <v>39.5</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>25.3</v>
+        <v>12</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -4185,27 +4229,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4215,101 +4259,109 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>42.96</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
           <t>34.24</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>19.09</t>
-        </is>
-      </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>29.06</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -4328,7 +4380,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Enrique Hernandez</t>
+          <t>Enrique Hernández</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4348,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4372,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>38.5</v>
+        <v>45</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,7 +4438,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4396,10 +4448,10 @@
         <v>39.5</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
         <v>78</v>
@@ -4409,39 +4461,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4584,8 +4632,16 @@
           <t>29.7</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -4599,12 +4655,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4624,12 +4680,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4648,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>36.6</v>
+        <v>42</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,62 +4718,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>33.9</v>
+        <v>17.3</v>
       </c>
       <c r="Q16" t="n">
         <v>39.5</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>12</v>
+        <v>14.1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4737,12 +4789,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4752,12 +4804,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,67 +4819,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>98.0168</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.3776</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.1083</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.3039</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -4860,8 +4912,16 @@
           <t>29.7</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -4875,12 +4935,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4900,12 +4960,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4924,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.7</v>
+        <v>36.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,65 +4998,61 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>16.6</v>
+        <v>11.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>34.7</v>
+        <v>35.6</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>5.1</v>
+        <v>23.7</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -5013,12 +5069,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5028,12 +5084,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5043,67 +5099,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -5136,8 +5192,16 @@
           <t>29.06</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -5176,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5200,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>30.2</v>
+        <v>36.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,7 +5278,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -5224,10 +5288,10 @@
         <v>35.6</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
@@ -5237,39 +5301,35 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -5412,8 +5472,16 @@
           <t>29.06</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -5427,12 +5495,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5452,12 +5520,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5476,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.6</v>
+        <v>35.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,62 +5558,58 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>5.4</v>
       </c>
       <c r="Q19" t="n">
         <v>35.6</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>17.3</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5565,12 +5629,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -5580,12 +5644,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5595,67 +5659,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -5688,8 +5752,16 @@
           <t>29.06</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -6054,12 +6126,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6078,11 +6150,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>57.4</v>
+        <v>63.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -6092,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6174,10 @@
         <v>39.5</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -6115,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -6290,8 +6358,16 @@
           <t>29.7</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -6330,12 +6406,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -6354,11 +6430,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55.4</v>
+        <v>61.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -6368,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6454,10 @@
         <v>39.5</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
@@ -6391,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -6566,8 +6638,16 @@
           <t>29.7</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -6606,12 +6686,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -6630,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>53.3</v>
+        <v>59.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6734,10 @@
         <v>35.6</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -6667,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6842,8 +6918,16 @@
           <t>29.06</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -6857,24 +6941,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -6882,31 +6966,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>49.6</v>
+        <v>55.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,65 +7004,61 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>45.7</v>
+        <v>50.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>39.5</v>
+        <v>35.6</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>48.3</v>
+        <v>63.3</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -6995,12 +7075,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -7010,12 +7090,12 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -7025,101 +7105,109 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>0.3329</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>74.25</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>44.59</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>31.29</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>29.27</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.1951</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>89.53</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
           <t>0.3296</t>
         </is>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>72.62</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>26.95</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>34.92</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>28.4</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>0.1727</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0.375</t>
-        </is>
-      </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+          <t>29.06</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -7133,12 +7221,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7158,12 +7246,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -7182,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>49.3</v>
+        <v>55.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,62 +7284,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>50.1</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
         <v>35.6</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>63.3</v>
+        <v>65.2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7276,22 +7360,22 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -7301,67 +7385,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -7394,8 +7478,16 @@
           <t>29.06</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -7409,24 +7501,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -7434,31 +7526,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>48.6</v>
+        <v>54.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,65 +7564,61 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.6</v>
+        <v>45.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>35.6</v>
+        <v>39.5</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>95.5</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>65.2</v>
+        <v>48.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -7547,27 +7635,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7577,101 +7665,109 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>29.06</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -7685,24 +7781,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -7710,31 +7806,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>47.5</v>
+        <v>52.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,65 +7844,61 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>47.1</v>
+        <v>32.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>35.6</v>
+        <v>39.5</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U8" t="n">
-        <v>13.3</v>
+        <v>29.2</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -7828,126 +7920,134 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>77.44</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>29.06</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -7961,24 +8061,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>571970</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -7986,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -7996,21 +8096,21 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>47.3</v>
+        <v>52.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,65 +8124,61 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>55.1</v>
+        <v>47.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>39.5</v>
+        <v>35.6</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>18</v>
+        <v>13.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -8099,12 +8195,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -8114,116 +8210,124 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.2892</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4781</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2366</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3565</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>77.44</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2347</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>29.06</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -8237,24 +8341,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -8262,31 +8366,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>45.3</v>
+        <v>51.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,65 +8404,61 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>32.7</v>
+        <v>38.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>39.5</v>
+        <v>35.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>29.2</v>
+        <v>25.3</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -8375,12 +8475,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -8390,12 +8490,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -8405,101 +8505,109 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+          <t>29.06</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -8513,24 +8621,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -8538,31 +8646,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>45.1</v>
+        <v>51.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,65 +8684,61 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>39.5</v>
+        <v>35.6</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>13</v>
+        <v>37.8</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -8656,22 +8760,22 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8681,101 +8785,109 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>36.44</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+          <t>29.06</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -8789,24 +8901,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -8814,31 +8926,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>44.8</v>
+        <v>51.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,65 +8964,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q12" t="n">
         <v>39.5</v>
       </c>
-      <c r="Q12" t="n">
-        <v>35.6</v>
-      </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>37.8</v>
+        <v>13</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -8932,22 +9040,22 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -8957,101 +9065,109 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>29.06</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -9090,12 +9206,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9114,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>44.3</v>
+        <v>49.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,7 +9244,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -9138,10 +9254,10 @@
         <v>39.5</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T13" t="n">
         <v>78</v>
@@ -9151,39 +9267,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9326,8 +9438,16 @@
           <t>29.7</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -9341,24 +9461,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -9366,31 +9486,31 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>43.8</v>
+        <v>47.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,65 +9524,61 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>38.2</v>
+        <v>33.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>35.6</v>
+        <v>39.5</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>25.3</v>
+        <v>12</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -9479,27 +9595,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9509,101 +9625,109 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>42.96</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
           <t>34.24</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>19.09</t>
-        </is>
-      </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>29.06</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -9622,7 +9746,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Enrique Hernandez</t>
+          <t>Enrique Hernández</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9642,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9666,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>38.5</v>
+        <v>45</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,7 +9804,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -9690,10 +9814,10 @@
         <v>39.5</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
         <v>78</v>
@@ -9703,39 +9827,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9878,8 +9998,16 @@
           <t>29.7</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -9893,12 +10021,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9918,12 +10046,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9942,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>36.6</v>
+        <v>42</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,62 +10084,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>33.9</v>
+        <v>17.3</v>
       </c>
       <c r="Q16" t="n">
         <v>39.5</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>12</v>
+        <v>14.1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10031,12 +10155,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10046,12 +10170,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,67 +10185,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>98.0168</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.3776</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.1083</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.3039</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -10154,8 +10278,16 @@
           <t>29.7</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -10169,12 +10301,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10194,12 +10326,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10218,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.7</v>
+        <v>36.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,65 +10364,61 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>16.6</v>
+        <v>11.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>34.7</v>
+        <v>35.6</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>5.1</v>
+        <v>23.7</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -10307,12 +10435,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -10322,12 +10450,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10337,67 +10465,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -10430,8 +10558,16 @@
           <t>29.06</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -10470,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10494,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>30.2</v>
+        <v>36.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,7 +10644,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -10518,10 +10654,10 @@
         <v>35.6</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
@@ -10531,39 +10667,35 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -10706,8 +10838,16 @@
           <t>29.06</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -10721,12 +10861,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10746,12 +10886,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -10770,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.6</v>
+        <v>35.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,62 +10924,58 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>5.4</v>
       </c>
       <c r="Q19" t="n">
         <v>35.6</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>17.3</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10859,12 +10995,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -10874,12 +11010,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -10889,67 +11025,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -10982,8 +11118,16 @@
           <t>29.06</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -768,11 +768,23 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>54.7</v>
+        <v>51.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -790,10 +802,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R2" t="n">
         <v>27.6</v>
@@ -802,7 +814,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U2" t="n">
         <v>37.8</v>
@@ -844,7 +856,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -881,7 +893,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -926,7 +938,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -954,12 +966,36 @@
           <t>0.2549</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
@@ -1008,11 +1044,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1026,14 +1074,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
         <v>48.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R3" t="n">
         <v>27.6</v>
@@ -1042,7 +1090,7 @@
         <v>95.5</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U3" t="n">
         <v>28.9</v>
@@ -1084,7 +1132,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -1121,7 +1169,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1194,12 +1242,36 @@
           <t>0.1639</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
@@ -1423,7 +1495,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>72.74</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1800,11 +1872,23 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>46.6</v>
+        <v>46.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1818,14 +1902,14 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
         <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>27.6</v>
@@ -1834,7 +1918,7 @@
         <v>71.7</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
         <v>54.9</v>
@@ -1876,7 +1960,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1913,7 +1997,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1986,12 +2070,36 @@
           <t>0.2134</t>
         </is>
       </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
@@ -2007,24 +2115,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -2037,14 +2145,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>46.4</v>
+        <v>43.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2058,26 +2178,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R7" t="n">
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2091,7 +2211,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2116,7 +2236,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -2133,12 +2253,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2148,12 +2268,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2163,75 +2283,99 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+          <t>0.1803</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
@@ -2247,24 +2391,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -2277,17 +2421,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2296,7 +2440,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.5</v>
+        <v>43.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2310,26 +2454,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R8" t="n">
         <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>10.1</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2343,7 +2487,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2385,12 +2529,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2400,12 +2544,12 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2415,97 +2559,97 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.57</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr"/>
@@ -3007,7 +3151,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -3351,24 +3495,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -3381,14 +3525,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3402,26 +3558,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>7.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R12" t="n">
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3435,7 +3591,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3460,7 +3616,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3477,12 +3633,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3492,12 +3648,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3507,75 +3663,99 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
@@ -3591,24 +3771,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -3621,17 +3801,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3640,7 +3820,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3654,26 +3834,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>20.9</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R13" t="n">
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3687,7 +3867,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3712,7 +3892,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -3729,12 +3909,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -3744,12 +3924,12 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3759,97 +3939,97 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
@@ -4143,24 +4323,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -4173,14 +4353,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>34.8</v>
+        <v>32.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4194,26 +4386,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10.6</v>
+        <v>13.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>32.5</v>
       </c>
       <c r="R15" t="n">
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>70.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4227,7 +4419,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -4252,7 +4444,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4274,7 +4466,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4289,7 +4481,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4299,75 +4491,99 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.151</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
+          <t>0.1287</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
@@ -4383,24 +4599,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -4413,17 +4629,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4432,7 +4648,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.5</v>
+        <v>31.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4446,26 +4662,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>13.7</v>
+        <v>15.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>72.7</v>
+        <v>19.5</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4479,7 +4695,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4521,27 +4737,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4551,97 +4767,97 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr"/>
@@ -4659,12 +4875,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4689,14 +4905,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>32.2</v>
+        <v>31.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4710,26 +4938,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>15.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -4743,7 +4971,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -4768,7 +4996,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -4785,27 +5013,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -4815,75 +5043,99 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
@@ -4932,11 +5184,23 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L18" t="n">
-        <v>31.8</v>
+        <v>31.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -4950,14 +5214,14 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
         <v>0.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R18" t="n">
         <v>27.6</v>
@@ -4966,7 +5230,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
         <v>15.3</v>
@@ -5008,7 +5272,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5045,7 +5309,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5118,12 +5382,36 @@
           <t>0.05</t>
         </is>
       </c>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
@@ -5172,11 +5460,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>29.4</v>
+        <v>27.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5197,7 +5497,7 @@
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.2</v>
+        <v>31.5</v>
       </c>
       <c r="R19" t="n">
         <v>27.6</v>
@@ -5248,7 +5548,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -5285,7 +5585,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5358,12 +5658,36 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
@@ -5738,11 +6062,23 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>54.7</v>
+        <v>51.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -5760,10 +6096,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R2" t="n">
         <v>27.6</v>
@@ -5772,7 +6108,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U2" t="n">
         <v>37.8</v>
@@ -5814,7 +6150,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -5851,7 +6187,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -5896,7 +6232,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -5924,12 +6260,36 @@
           <t>0.2549</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
@@ -5978,11 +6338,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -5996,14 +6368,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
         <v>48.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R3" t="n">
         <v>27.6</v>
@@ -6012,7 +6384,7 @@
         <v>95.5</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U3" t="n">
         <v>28.9</v>
@@ -6054,7 +6426,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -6091,7 +6463,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -6164,12 +6536,36 @@
           <t>0.1639</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
@@ -6393,7 +6789,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>72.74</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -6770,11 +7166,23 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>46.6</v>
+        <v>46.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -6788,14 +7196,14 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
         <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>27.6</v>
@@ -6804,7 +7212,7 @@
         <v>71.7</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
         <v>54.9</v>
@@ -6846,7 +7254,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -6883,7 +7291,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -6956,12 +7364,36 @@
           <t>0.2134</t>
         </is>
       </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
@@ -6977,24 +7409,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -7007,14 +7439,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>46.4</v>
+        <v>43.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7028,26 +7472,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R7" t="n">
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -7061,7 +7505,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -7086,7 +7530,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -7103,12 +7547,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -7118,12 +7562,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7133,75 +7577,99 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+          <t>0.1803</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
@@ -7217,24 +7685,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -7247,17 +7715,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7266,7 +7734,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.5</v>
+        <v>43.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7280,26 +7748,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R8" t="n">
         <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>10.1</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -7313,7 +7781,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -7355,12 +7823,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -7370,12 +7838,12 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -7385,97 +7853,97 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.57</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr"/>
@@ -7977,7 +8445,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -8321,24 +8789,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -8351,14 +8819,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8372,26 +8852,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>7.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R12" t="n">
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -8405,7 +8885,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -8430,7 +8910,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -8447,12 +8927,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -8462,12 +8942,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -8477,75 +8957,99 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
@@ -8561,24 +9065,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -8591,17 +9095,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -8610,7 +9114,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -8624,26 +9128,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>20.9</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R13" t="n">
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -8657,7 +9161,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -8682,7 +9186,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -8699,12 +9203,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -8714,12 +9218,12 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -8729,97 +9233,97 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
@@ -9113,24 +9617,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -9143,14 +9647,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>34.8</v>
+        <v>32.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9164,26 +9680,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10.6</v>
+        <v>13.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>32.5</v>
       </c>
       <c r="R15" t="n">
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>70.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -9197,7 +9713,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -9222,7 +9738,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -9244,7 +9760,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9259,7 +9775,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9269,75 +9785,99 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.151</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
+          <t>0.1287</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
@@ -9353,24 +9893,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -9383,17 +9923,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -9402,7 +9942,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.5</v>
+        <v>31.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9416,26 +9956,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>13.7</v>
+        <v>15.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>72.7</v>
+        <v>19.5</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -9449,7 +9989,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -9491,27 +10031,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -9521,97 +10061,97 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr"/>
@@ -9629,12 +10169,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -9659,14 +10199,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>32.2</v>
+        <v>31.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -9680,26 +10232,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>15.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -9713,7 +10265,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -9738,7 +10290,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -9755,27 +10307,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -9785,75 +10337,99 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
@@ -9902,11 +10478,23 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L18" t="n">
-        <v>31.8</v>
+        <v>31.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -9920,14 +10508,14 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
         <v>0.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R18" t="n">
         <v>27.6</v>
@@ -9936,7 +10524,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
         <v>15.3</v>
@@ -9978,7 +10566,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -10015,7 +10603,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10088,12 +10676,36 @@
           <t>0.05</t>
         </is>
       </c>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
@@ -10142,11 +10754,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>29.4</v>
+        <v>27.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10167,7 +10791,7 @@
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.2</v>
+        <v>31.5</v>
       </c>
       <c r="R19" t="n">
         <v>27.6</v>
@@ -10218,7 +10842,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -10255,7 +10879,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -10328,12 +10952,36 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,12 +760,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.5</v>
+        <v>54.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1036,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1312,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.9</v>
+        <v>51.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>34.3</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1373,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1548,8 +1552,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1588,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1612,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.9</v>
+        <v>49.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1636,10 +1648,10 @@
         <v>34.3</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1649,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1824,8 +1832,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1844,7 +1860,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1864,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1888,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.2</v>
+        <v>49.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,7 +1918,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1912,10 +1928,10 @@
         <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S6" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -1925,39 +1941,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2100,8 +2112,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2140,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2164,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.5</v>
+        <v>46.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,7 +2198,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2188,10 +2208,10 @@
         <v>34.3</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -2201,39 +2221,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2376,8 +2392,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2396,7 +2420,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2416,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2440,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.3</v>
+        <v>46.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,7 +2478,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2464,10 +2488,10 @@
         <v>32</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S8" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
@@ -2477,39 +2501,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2652,8 +2672,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2672,7 +2700,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2692,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2716,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.7</v>
+        <v>44.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2740,10 +2768,10 @@
         <v>32.5</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -2753,39 +2781,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2928,8 +2952,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2968,12 +3000,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2992,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>38.5</v>
+        <v>43.2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3048,10 @@
         <v>32.5</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S10" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -3029,39 +3061,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3204,8 +3232,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3219,12 +3255,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3244,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.1</v>
+        <v>40.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,65 +3318,61 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>32.5</v>
+        <v>34.3</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>36.3</v>
+        <v>12</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3357,7 +3389,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -3367,17 +3399,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3387,67 +3419,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>71.08</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -3480,8 +3512,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3495,12 +3535,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3520,12 +3560,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3544,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>35.5</v>
+        <v>38.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,65 +3598,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>20.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="n">
         <v>34.3</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>12</v>
+        <v>43.1</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3633,12 +3669,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3648,7 +3684,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -3663,67 +3699,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -3756,8 +3792,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3796,12 +3840,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3820,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.2</v>
+        <v>37.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,7 +3878,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3844,10 +3888,10 @@
         <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S13" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -3857,39 +3901,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4032,8 +4072,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4047,24 +4095,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -4072,22 +4120,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4096,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.1</v>
+        <v>35.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,62 +4158,58 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S14" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>43.1</v>
+        <v>15.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4185,7 +4229,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -4200,12 +4244,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4215,101 +4259,109 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4348,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4372,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.5</v>
+        <v>35.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,7 +4438,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4396,10 +4448,10 @@
         <v>32.5</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -4409,39 +4461,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4584,8 +4632,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4599,12 +4655,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4624,12 +4680,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4648,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.8</v>
+        <v>34.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,62 +4718,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>15.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
         <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4737,27 +4789,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,67 +4819,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -4860,8 +4912,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4875,12 +4935,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4900,12 +4960,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4924,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.7</v>
+        <v>34.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,62 +4998,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>10.6</v>
+        <v>15.4</v>
       </c>
       <c r="Q17" t="n">
         <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5013,27 +5069,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5043,67 +5099,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -5136,8 +5192,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -5151,24 +5215,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -5176,22 +5240,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5200,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>31.3</v>
+        <v>33.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,62 +5278,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>7.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S18" t="n">
-        <v>81.90000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5289,12 +5349,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5304,12 +5364,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5319,101 +5379,109 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>28.96</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -5452,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5476,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.3</v>
+        <v>30.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5500,10 +5568,10 @@
         <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -5513,39 +5581,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5688,8 +5752,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6054,12 +6126,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6078,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.5</v>
+        <v>54.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6174,10 @@
         <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -6115,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6290,8 +6358,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6330,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6354,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6454,10 @@
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6391,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6638,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6606,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6630,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.9</v>
+        <v>51.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6734,10 @@
         <v>34.3</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -6667,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6842,8 +6918,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6882,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6906,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.9</v>
+        <v>49.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -6930,10 +7014,10 @@
         <v>34.3</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -6943,39 +7027,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7118,8 +7198,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7138,7 +7226,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7158,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7182,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.2</v>
+        <v>49.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,7 +7284,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7206,10 +7294,10 @@
         <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S6" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -7219,39 +7307,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7394,8 +7478,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7434,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7458,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.5</v>
+        <v>46.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,7 +7564,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -7482,10 +7574,10 @@
         <v>34.3</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -7495,39 +7587,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7670,8 +7758,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7690,7 +7786,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7710,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7734,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.3</v>
+        <v>46.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,7 +7844,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7758,10 +7854,10 @@
         <v>32</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S8" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
@@ -7771,39 +7867,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7946,8 +8038,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7966,7 +8066,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7986,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8010,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.7</v>
+        <v>44.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,7 +8124,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8034,10 +8134,10 @@
         <v>32.5</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -8047,39 +8147,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8222,8 +8318,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8262,12 +8366,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8286,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>38.5</v>
+        <v>43.2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8414,10 @@
         <v>32.5</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S10" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -8323,39 +8427,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8498,8 +8598,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8513,12 +8621,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8538,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.1</v>
+        <v>40.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,65 +8684,61 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>32.5</v>
+        <v>34.3</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>36.3</v>
+        <v>12</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -8651,7 +8755,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -8661,17 +8765,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8681,67 +8785,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>71.08</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -8774,8 +8878,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8789,12 +8901,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -8814,12 +8926,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -8838,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>35.5</v>
+        <v>38.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,65 +8964,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>20.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="n">
         <v>34.3</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>12</v>
+        <v>43.1</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -8927,12 +9035,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -8942,7 +9050,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -8957,67 +9065,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -9050,8 +9158,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9090,12 +9206,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9114,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.2</v>
+        <v>37.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,7 +9244,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -9138,10 +9254,10 @@
         <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S13" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -9151,39 +9267,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9326,8 +9438,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9341,24 +9461,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -9366,22 +9486,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -9390,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.1</v>
+        <v>35.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,62 +9524,58 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S14" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>43.1</v>
+        <v>15.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9479,7 +9595,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -9494,12 +9610,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9509,101 +9625,109 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9642,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9666,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.5</v>
+        <v>35.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,7 +9804,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -9690,10 +9814,10 @@
         <v>32.5</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -9703,39 +9827,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9878,8 +9998,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9893,12 +10021,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9918,12 +10046,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9942,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.8</v>
+        <v>34.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,62 +10084,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>15.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
         <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10031,27 +10155,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,67 +10185,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -10154,8 +10278,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10169,12 +10301,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10194,12 +10326,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10218,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.7</v>
+        <v>34.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,62 +10364,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>10.6</v>
+        <v>15.4</v>
       </c>
       <c r="Q17" t="n">
         <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10307,27 +10435,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10337,67 +10465,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -10430,8 +10558,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10445,24 +10581,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -10470,22 +10606,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -10494,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>31.3</v>
+        <v>33.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,62 +10644,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>7.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S18" t="n">
-        <v>81.90000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10583,12 +10715,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10598,12 +10730,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10613,101 +10745,109 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>28.96</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10746,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10770,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.3</v>
+        <v>30.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -10794,10 +10934,10 @@
         <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -10807,39 +10947,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10982,8 +11118,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Progressive Field</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -755,7 +755,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00:00Z</t>
+          <t>2026-10-18T00:08:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.5</v>
+        <v>53.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S2" t="n">
         <v>92.09999999999999</v>
@@ -996,8 +996,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1036,7 +1044,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1060,7 +1068,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>51.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1084,7 +1092,7 @@
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S3" t="n">
         <v>95.5</v>
@@ -1272,8 +1280,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1312,7 +1328,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1336,7 +1352,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.9</v>
+        <v>51.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1366,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1376,10 @@
         <v>34.3</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1373,39 +1389,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1548,8 +1560,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1588,7 +1608,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1612,7 +1632,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.9</v>
+        <v>49.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,7 +1646,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1636,10 +1656,10 @@
         <v>34.3</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1649,39 +1669,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1824,8 +1840,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1864,7 +1888,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1888,7 +1912,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>43.5</v>
+        <v>46</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,7 +1926,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1912,10 +1936,10 @@
         <v>34.3</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -1925,39 +1949,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2100,8 +2120,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2140,7 +2168,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2164,7 +2192,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.3</v>
+        <v>45.1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2188,7 +2216,7 @@
         <v>32</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S7" t="n">
         <v>88.7</v>
@@ -2376,8 +2404,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2416,7 +2452,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2440,7 +2476,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.3</v>
+        <v>45.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2464,7 +2500,7 @@
         <v>32</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S8" t="n">
         <v>90.40000000000001</v>
@@ -2652,8 +2688,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2672,7 +2716,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2692,7 +2736,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2716,7 +2760,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.7</v>
+        <v>44.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,7 +2774,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2740,10 +2784,10 @@
         <v>32.5</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -2753,39 +2797,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2928,8 +2968,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2968,7 +3016,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2992,7 +3040,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40.2</v>
+        <v>42.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3054,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3064,10 @@
         <v>32.5</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -3029,39 +3077,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3204,8 +3248,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3244,7 +3296,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3320,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>37.1</v>
+        <v>39.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,7 +3334,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3292,10 +3344,10 @@
         <v>34.3</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -3305,39 +3357,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -3480,8 +3528,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3520,7 +3576,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3544,7 +3600,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>35.1</v>
+        <v>37.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,7 +3614,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3568,10 +3624,10 @@
         <v>34.3</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -3581,39 +3637,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3756,8 +3808,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3796,7 +3856,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3820,7 +3880,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.8</v>
+        <v>36.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3844,7 +3904,7 @@
         <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S13" t="n">
         <v>81.90000000000001</v>
@@ -4032,8 +4092,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4072,7 +4140,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4096,7 +4164,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.5</v>
+        <v>34.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,7 +4178,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4120,10 +4188,10 @@
         <v>32.5</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -4133,39 +4201,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4308,8 +4372,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4323,24 +4395,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -4348,7 +4420,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4358,12 +4430,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4372,7 +4444,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.7</v>
+        <v>33</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,62 +4458,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>7.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>38.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4461,12 +4529,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4476,12 +4544,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4491,101 +4559,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>28.96</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4599,24 +4675,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -4624,7 +4700,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4634,12 +4710,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4648,7 +4724,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.5</v>
+        <v>32.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,26 +4738,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.1</v>
+        <v>23.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S16" t="n">
         <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>0.8</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4737,12 +4813,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4752,12 +4828,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,101 +4843,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>98.4476</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1223</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2522</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1044</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4900,7 +4984,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4924,7 +5008,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.9</v>
+        <v>31.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4948,7 +5032,7 @@
         <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S17" t="n">
         <v>71.7</v>
@@ -5136,8 +5220,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -5176,7 +5268,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5200,7 +5292,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>29.8</v>
+        <v>31.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5224,7 +5316,7 @@
         <v>32</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S18" t="n">
         <v>59.8</v>
@@ -5412,8 +5504,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -5452,7 +5552,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5476,7 +5576,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.3</v>
+        <v>29.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5500,7 +5600,7 @@
         <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S19" t="n">
         <v>40.2</v>
@@ -5688,8 +5788,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6054,7 +6162,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6078,7 +6186,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.5</v>
+        <v>53.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6102,7 +6210,7 @@
         <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S2" t="n">
         <v>92.09999999999999</v>
@@ -6290,8 +6398,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6330,7 +6446,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6354,7 +6470,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>51.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6378,7 +6494,7 @@
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S3" t="n">
         <v>95.5</v>
@@ -6566,8 +6682,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6606,7 +6730,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6630,7 +6754,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.9</v>
+        <v>51.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6768,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6778,10 @@
         <v>34.3</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -6667,39 +6791,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6842,8 +6962,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6882,7 +7010,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6906,7 +7034,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.9</v>
+        <v>49.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,7 +7048,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -6930,10 +7058,10 @@
         <v>34.3</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -6943,39 +7071,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7118,8 +7242,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7158,7 +7290,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7182,7 +7314,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>43.5</v>
+        <v>46</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,7 +7328,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7206,10 +7338,10 @@
         <v>34.3</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -7219,39 +7351,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7394,8 +7522,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7434,7 +7570,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7458,7 +7594,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.3</v>
+        <v>45.1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7482,7 +7618,7 @@
         <v>32</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S7" t="n">
         <v>88.7</v>
@@ -7670,8 +7806,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7710,7 +7854,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7734,7 +7878,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.3</v>
+        <v>45.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7758,7 +7902,7 @@
         <v>32</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S8" t="n">
         <v>90.40000000000001</v>
@@ -7946,8 +8090,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7966,7 +8118,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7986,7 +8138,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8010,7 +8162,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.7</v>
+        <v>44.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,7 +8176,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8034,10 +8186,10 @@
         <v>32.5</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -8047,39 +8199,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8222,8 +8370,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8262,7 +8418,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8286,7 +8442,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40.2</v>
+        <v>42.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8456,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8466,10 @@
         <v>32.5</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -8323,39 +8479,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8498,8 +8650,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8538,7 +8698,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8722,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>37.1</v>
+        <v>39.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,7 +8736,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8586,10 +8746,10 @@
         <v>34.3</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -8599,39 +8759,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -8774,8 +8930,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8814,7 +8978,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8838,7 +9002,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>35.1</v>
+        <v>37.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,7 +9016,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -8862,10 +9026,10 @@
         <v>34.3</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -8875,39 +9039,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9050,8 +9210,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9090,7 +9258,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9114,7 +9282,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.8</v>
+        <v>36.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9138,7 +9306,7 @@
         <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S13" t="n">
         <v>81.90000000000001</v>
@@ -9326,8 +9494,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9366,7 +9542,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9390,7 +9566,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.5</v>
+        <v>34.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,7 +9580,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9414,10 +9590,10 @@
         <v>32.5</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -9427,39 +9603,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9602,8 +9774,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9617,24 +9797,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -9642,7 +9822,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9652,12 +9832,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -9666,7 +9846,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.7</v>
+        <v>33</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,62 +9860,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>7.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>38.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9755,12 +9931,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9770,12 +9946,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9785,101 +9961,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>28.96</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9893,24 +10077,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -9918,7 +10102,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -9928,12 +10112,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -9942,7 +10126,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.5</v>
+        <v>32.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,26 +10140,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.1</v>
+        <v>23.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S16" t="n">
         <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>0.8</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -10031,12 +10215,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10046,12 +10230,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,101 +10245,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>98.4476</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1223</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2522</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1044</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10194,7 +10386,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10218,7 +10410,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.9</v>
+        <v>31.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10242,7 +10434,7 @@
         <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S17" t="n">
         <v>71.7</v>
@@ -10430,8 +10622,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10470,7 +10670,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10494,7 +10694,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>29.8</v>
+        <v>31.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10518,7 +10718,7 @@
         <v>32</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S18" t="n">
         <v>59.8</v>
@@ -10706,8 +10906,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10746,7 +10954,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10770,7 +10978,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.3</v>
+        <v>29.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10794,7 +11002,7 @@
         <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S19" t="n">
         <v>40.2</v>
@@ -10982,8 +11190,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Progressive Field</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>53.3</v>
+        <v>53.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -811,7 +811,7 @@
         <v>39.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1068,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.8</v>
+        <v>52.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1095,7 +1091,7 @@
         <v>39.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1105,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1863,24 +1855,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -1893,17 +1885,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1912,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46</v>
+        <v>48.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1930,22 +1922,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>39.6</v>
       </c>
       <c r="S6" t="n">
-        <v>86.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>10.1</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1959,7 +1951,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1997,27 +1989,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2027,97 +2019,97 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -2143,24 +2135,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -2173,17 +2165,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2192,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>45.1</v>
+        <v>46</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2206,62 +2198,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R7" t="n">
         <v>39.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2281,12 +2269,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2296,12 +2284,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2311,97 +2299,97 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.57</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -2427,12 +2415,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2457,7 +2445,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2476,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>45.1</v>
+        <v>45.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2490,11 +2478,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
         <v>32</v>
@@ -2503,49 +2491,45 @@
         <v>39.6</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2565,12 +2549,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2580,7 +2564,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2595,67 +2579,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.57</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -3831,12 +3815,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3880,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3894,11 +3878,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
         <v>32</v>
@@ -3907,49 +3891,45 @@
         <v>39.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3969,27 +3949,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3999,67 +3979,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -4115,24 +4095,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -4145,17 +4125,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4164,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>34.9</v>
+        <v>35.2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4178,26 +4158,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>13.7</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="R14" t="n">
         <v>39.6</v>
       </c>
       <c r="S14" t="n">
-        <v>44.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>72.7</v>
+        <v>15.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4211,7 +4191,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4249,27 +4229,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4279,97 +4259,97 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -4395,12 +4375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4425,7 +4405,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -4444,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>33</v>
+        <v>34.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4458,26 +4438,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>7.1</v>
+        <v>13.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>34.3</v>
+        <v>32.5</v>
       </c>
       <c r="R15" t="n">
         <v>39.6</v>
       </c>
       <c r="S15" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>38.3</v>
+        <v>72.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4491,7 +4471,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -4529,27 +4509,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4559,67 +4539,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -4675,12 +4655,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4705,7 +4685,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4724,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.5</v>
+        <v>34.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4738,11 +4718,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>23.3</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
         <v>32</v>
@@ -4751,49 +4731,45 @@
         <v>39.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
         <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4813,22 +4789,22 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -4843,67 +4819,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -4959,12 +4935,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4989,7 +4965,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5008,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.7</v>
+        <v>34.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5022,11 +4998,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q17" t="n">
         <v>32</v>
@@ -5035,49 +5011,45 @@
         <v>39.6</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5097,12 +5069,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5112,7 +5084,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5127,67 +5099,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -5243,24 +5215,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -5273,17 +5245,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5292,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>31.6</v>
+        <v>33</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5306,62 +5278,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>7.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R18" t="n">
         <v>39.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5381,27 +5349,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5411,97 +5379,97 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
@@ -5576,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.1</v>
+        <v>29.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5590,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5603,7 +5571,7 @@
         <v>39.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -5613,39 +5581,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6167,7 +6131,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6186,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>53.3</v>
+        <v>53.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6200,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6213,7 +6177,7 @@
         <v>39.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -6223,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6470,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.8</v>
+        <v>52.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6484,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6497,7 +6457,7 @@
         <v>39.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6507,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7265,24 +7221,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -7295,17 +7251,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -7314,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46</v>
+        <v>48.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7332,22 +7288,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>39.6</v>
       </c>
       <c r="S6" t="n">
-        <v>86.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>10.1</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -7361,7 +7317,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -7399,27 +7355,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -7429,97 +7385,97 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -7545,24 +7501,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -7575,17 +7531,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -7594,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>45.1</v>
+        <v>46</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7608,62 +7564,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R7" t="n">
         <v>39.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7683,12 +7635,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -7698,12 +7650,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7713,97 +7665,97 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.57</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -7829,12 +7781,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7859,7 +7811,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7878,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>45.1</v>
+        <v>45.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7892,11 +7844,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
         <v>32</v>
@@ -7905,49 +7857,45 @@
         <v>39.6</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7967,12 +7915,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -7982,7 +7930,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -7997,67 +7945,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.57</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -9233,12 +9181,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9282,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9296,11 +9244,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
         <v>32</v>
@@ -9309,49 +9257,45 @@
         <v>39.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9371,27 +9315,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9401,67 +9345,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -9517,24 +9461,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -9547,17 +9491,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -9566,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>34.9</v>
+        <v>35.2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9580,26 +9524,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>13.7</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="R14" t="n">
         <v>39.6</v>
       </c>
       <c r="S14" t="n">
-        <v>44.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>72.7</v>
+        <v>15.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -9613,7 +9557,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -9651,27 +9595,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9681,97 +9625,97 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -9797,12 +9741,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9827,7 +9771,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -9846,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>33</v>
+        <v>34.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9860,26 +9804,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>7.1</v>
+        <v>13.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>34.3</v>
+        <v>32.5</v>
       </c>
       <c r="R15" t="n">
         <v>39.6</v>
       </c>
       <c r="S15" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>38.3</v>
+        <v>72.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -9893,7 +9837,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -9931,27 +9875,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9961,67 +9905,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -10077,12 +10021,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10107,7 +10051,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -10126,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.5</v>
+        <v>34.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10140,11 +10084,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>23.3</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
         <v>32</v>
@@ -10153,49 +10097,45 @@
         <v>39.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
         <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10215,22 +10155,22 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -10245,67 +10185,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -10361,12 +10301,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10391,7 +10331,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10410,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.7</v>
+        <v>34.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10424,11 +10364,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q17" t="n">
         <v>32</v>
@@ -10437,49 +10377,45 @@
         <v>39.6</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10499,12 +10435,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -10514,7 +10450,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -10529,67 +10465,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -10645,24 +10581,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -10675,17 +10611,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -10694,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>31.6</v>
+        <v>33</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10708,62 +10644,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>7.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R18" t="n">
         <v>39.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10783,27 +10715,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10813,97 +10745,97 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
@@ -10978,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.1</v>
+        <v>29.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10992,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -11005,7 +10937,7 @@
         <v>39.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -11015,39 +10947,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>53.7</v>
+        <v>52.8</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52.4</v>
+        <v>51.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>51.3</v>
+        <v>50.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>34.3</v>
       </c>
       <c r="R4" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S4" t="n">
         <v>94.90000000000001</v>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>49.3</v>
+        <v>48.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>34.3</v>
       </c>
       <c r="R5" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S5" t="n">
         <v>96.59999999999999</v>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>48.6</v>
+        <v>47.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>34.3</v>
       </c>
       <c r="R7" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S7" t="n">
         <v>86.40000000000001</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>45.7</v>
+        <v>44.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>32</v>
       </c>
       <c r="R8" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.2</v>
+        <v>43.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>32.5</v>
       </c>
       <c r="R9" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>42.6</v>
+        <v>41.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>32.5</v>
       </c>
       <c r="R10" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>39.6</v>
+        <v>38.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>34.3</v>
       </c>
       <c r="R11" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>37.5</v>
+        <v>36.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>34.3</v>
       </c>
       <c r="R12" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S12" t="n">
         <v>93.2</v>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>36.5</v>
+        <v>35.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.2</v>
+        <v>34.2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>32</v>
       </c>
       <c r="R14" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S14" t="n">
         <v>96.59999999999999</v>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>34.9</v>
+        <v>33.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>32.5</v>
       </c>
       <c r="R15" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S15" t="n">
         <v>44.8</v>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>34.2</v>
+        <v>33.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -4914,12 +4914,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>34.2</v>
+        <v>33.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S17" t="n">
         <v>52.4</v>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>34.3</v>
       </c>
       <c r="R18" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.7</v>
+        <v>28.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>53.7</v>
+        <v>52.8</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52.4</v>
+        <v>51.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>51.3</v>
+        <v>50.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>34.3</v>
       </c>
       <c r="R4" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S4" t="n">
         <v>94.90000000000001</v>
@@ -6920,12 +6920,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>49.3</v>
+        <v>48.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>34.3</v>
       </c>
       <c r="R5" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S5" t="n">
         <v>96.59999999999999</v>
@@ -7200,12 +7200,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>48.6</v>
+        <v>47.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>34.3</v>
       </c>
       <c r="R7" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S7" t="n">
         <v>86.40000000000001</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>45.7</v>
+        <v>44.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>32</v>
       </c>
       <c r="R8" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.2</v>
+        <v>43.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>32.5</v>
       </c>
       <c r="R9" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -8320,12 +8320,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>42.6</v>
+        <v>41.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>32.5</v>
       </c>
       <c r="R10" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -8600,12 +8600,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>39.6</v>
+        <v>38.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>34.3</v>
       </c>
       <c r="R11" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -8880,12 +8880,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>37.5</v>
+        <v>36.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>34.3</v>
       </c>
       <c r="R12" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S12" t="n">
         <v>93.2</v>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>36.5</v>
+        <v>35.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -9440,12 +9440,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.2</v>
+        <v>34.2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>32</v>
       </c>
       <c r="R14" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S14" t="n">
         <v>96.59999999999999</v>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>34.9</v>
+        <v>33.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>32.5</v>
       </c>
       <c r="R15" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S15" t="n">
         <v>44.8</v>
@@ -10000,12 +10000,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>34.2</v>
+        <v>33.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>34.2</v>
+        <v>33.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S17" t="n">
         <v>52.4</v>
@@ -10560,12 +10560,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>34.3</v>
       </c>
       <c r="R18" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -10840,12 +10840,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.7</v>
+        <v>28.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11120,12 +11120,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1219,7 +1219,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>72.74</t>
+          <t>72.67</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.57</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -3698,12 +3698,12 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>72.74</t>
+          <t>72.67</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.57</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,12 +760,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.6</v>
+        <v>54</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1036,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>47.5</v>
+        <v>50.1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>28.5</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1312,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>45.5</v>
+        <v>48.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>28.5</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -1373,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1548,8 +1552,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1588,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1612,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>44.7</v>
+        <v>47.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1636,10 +1648,10 @@
         <v>21.5</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -1649,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1824,8 +1832,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1839,12 +1855,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1864,12 +1880,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1888,76 +1904,72 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Watch List</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Premium Lineup Spot, Platoon Edge</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
         <v>43.3</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Longshot</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Watch List</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>41</v>
       </c>
       <c r="Q6" t="n">
         <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>20.9</v>
+        <v>0</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1977,12 +1989,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1992,7 +2004,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2007,67 +2019,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2100,8 +2112,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2115,12 +2135,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2140,12 +2160,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2164,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.3</v>
+        <v>46</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,62 +2198,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
         <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T7" t="n">
         <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2253,12 +2269,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2268,7 +2284,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2283,67 +2299,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -2376,8 +2392,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2416,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2440,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>42.1</v>
+        <v>44.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,7 +2478,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2464,10 +2488,10 @@
         <v>28.5</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -2477,39 +2501,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2652,8 +2672,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2672,7 +2700,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2692,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2716,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>40.4</v>
+        <v>43</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2740,10 +2768,10 @@
         <v>26.9</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -2753,39 +2781,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2928,8 +2952,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2968,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2992,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>38.8</v>
+        <v>41.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3048,10 @@
         <v>26.9</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -3029,39 +3061,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3204,8 +3232,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3244,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>35.7</v>
+        <v>38.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,7 +3318,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3292,10 +3328,10 @@
         <v>28.5</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -3305,39 +3341,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -3480,8 +3512,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3495,24 +3535,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -3520,31 +3560,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34.8</v>
+        <v>36.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,62 +3598,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>70.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3633,27 +3669,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3663,101 +3699,109 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3771,24 +3815,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -3796,31 +3840,31 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>33.7</v>
+        <v>36</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,62 +3878,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.9</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S13" t="n">
-        <v>88.7</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>43.1</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3909,27 +3949,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3939,101 +3979,109 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>23.38</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4072,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4096,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>31.1</v>
+        <v>33.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,7 +4158,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4120,10 +4168,10 @@
         <v>26.9</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -4133,39 +4181,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4308,8 +4352,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4323,24 +4375,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -4348,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4358,21 +4410,21 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.7</v>
+        <v>31.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,62 +4438,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>7.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>38.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4461,12 +4509,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4476,12 +4524,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4491,101 +4539,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4599,12 +4655,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4624,12 +4680,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4648,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>29.8</v>
+        <v>29.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,62 +4718,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>12.8</v>
+        <v>11.6</v>
       </c>
       <c r="Q16" t="n">
         <v>21.5</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
         <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4742,17 +4794,17 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -4767,67 +4819,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -4860,8 +4912,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4875,24 +4935,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -4900,31 +4960,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.1</v>
+        <v>28.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,62 +4998,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>7.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>38.3</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5013,12 +5069,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5028,12 +5084,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5043,101 +5099,109 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>23.38</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -5151,12 +5215,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5176,12 +5240,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5200,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>24.7</v>
+        <v>28.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,62 +5278,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>7.8</v>
       </c>
       <c r="Q18" t="n">
         <v>21.5</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5294,7 +5354,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5304,7 +5364,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -5319,67 +5379,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -5412,8 +5472,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -5452,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5476,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>24.6</v>
+        <v>27.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5500,10 +5568,10 @@
         <v>20.1</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -5513,39 +5581,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5688,8 +5752,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6054,12 +6126,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6078,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.6</v>
+        <v>54</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6174,10 @@
         <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -6115,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6290,8 +6358,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6330,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6354,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>47.5</v>
+        <v>50.1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6454,10 @@
         <v>28.5</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -6391,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6638,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6606,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6630,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>45.5</v>
+        <v>48.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6734,10 @@
         <v>28.5</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -6667,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -6842,8 +6918,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6882,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6906,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>44.7</v>
+        <v>47.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -6930,10 +7014,10 @@
         <v>21.5</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -6943,39 +7027,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7118,8 +7198,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7133,12 +7221,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7158,12 +7246,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -7182,76 +7270,72 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Watch List</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Premium Lineup Spot, Platoon Edge</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
         <v>43.3</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Longshot</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Watch List</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>41</v>
       </c>
       <c r="Q6" t="n">
         <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>20.9</v>
+        <v>0</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7271,12 +7355,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -7286,7 +7370,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -7301,67 +7385,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -7394,8 +7478,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7409,12 +7501,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7434,12 +7526,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -7458,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.3</v>
+        <v>46</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,62 +7564,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
         <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T7" t="n">
         <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7547,12 +7635,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -7562,7 +7650,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -7577,67 +7665,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -7670,8 +7758,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7710,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7734,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>42.1</v>
+        <v>44.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,7 +7844,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7758,10 +7854,10 @@
         <v>28.5</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -7771,39 +7867,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7946,8 +8038,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7966,7 +8066,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7986,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8010,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>40.4</v>
+        <v>43</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,7 +8124,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8034,10 +8134,10 @@
         <v>26.9</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -8047,39 +8147,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8222,8 +8318,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8262,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8286,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>38.8</v>
+        <v>41.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8414,10 @@
         <v>26.9</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -8323,39 +8427,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8498,8 +8598,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8538,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>35.7</v>
+        <v>38.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,7 +8684,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8586,10 +8694,10 @@
         <v>28.5</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -8599,39 +8707,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -8774,8 +8878,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8789,24 +8901,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -8814,31 +8926,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34.8</v>
+        <v>36.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,62 +8964,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>70.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8927,27 +9035,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -8957,101 +9065,109 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9065,24 +9181,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -9090,31 +9206,31 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>33.7</v>
+        <v>36</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,62 +9244,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.9</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S13" t="n">
-        <v>88.7</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>43.1</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9203,27 +9315,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9233,101 +9345,109 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>23.38</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9366,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9390,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>31.1</v>
+        <v>33.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,7 +9524,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9414,10 +9534,10 @@
         <v>26.9</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -9427,39 +9547,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9602,8 +9718,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9617,24 +9741,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -9642,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9652,21 +9776,21 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.7</v>
+        <v>31.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,62 +9804,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>7.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>38.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9755,12 +9875,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9770,12 +9890,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9785,101 +9905,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9893,12 +10021,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9918,12 +10046,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9942,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>29.8</v>
+        <v>29.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,62 +10084,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>12.8</v>
+        <v>11.6</v>
       </c>
       <c r="Q16" t="n">
         <v>21.5</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
         <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10036,17 +10160,17 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -10061,67 +10185,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -10154,8 +10278,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10169,24 +10301,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -10194,31 +10326,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.1</v>
+        <v>28.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,62 +10364,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>7.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>38.3</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10307,12 +10435,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -10322,12 +10450,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10337,101 +10465,109 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>23.38</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10445,12 +10581,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10470,12 +10606,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10494,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>24.7</v>
+        <v>28.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,62 +10644,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>7.8</v>
       </c>
       <c r="Q18" t="n">
         <v>21.5</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10588,7 +10720,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10598,7 +10730,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -10613,67 +10745,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -10706,8 +10838,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10746,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10770,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>24.6</v>
+        <v>27.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -10794,10 +10934,10 @@
         <v>20.1</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -10807,39 +10947,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10982,8 +11118,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Progressive Field</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>54</v>
+        <v>54.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>28.5</v>
       </c>
       <c r="R3" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S3" t="n">
         <v>94.90000000000001</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.1</v>
+        <v>48.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>28.5</v>
       </c>
       <c r="R4" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S4" t="n">
         <v>96.59999999999999</v>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>47.4</v>
+        <v>47.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>21.5</v>
       </c>
       <c r="R5" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.2</v>
+        <v>46.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46</v>
+        <v>46.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S7" t="n">
         <v>93.2</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>44.8</v>
+        <v>45.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>28.5</v>
       </c>
       <c r="R8" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S8" t="n">
         <v>86.40000000000001</v>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>43</v>
+        <v>43.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>26.9</v>
       </c>
       <c r="R9" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>41.5</v>
+        <v>41.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>26.9</v>
       </c>
       <c r="R10" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.4</v>
+        <v>38.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>28.5</v>
       </c>
       <c r="R11" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>36.4</v>
+        <v>36.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>28.5</v>
       </c>
       <c r="R12" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S12" t="n">
         <v>93.2</v>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>36</v>
+        <v>36.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>21.5</v>
       </c>
       <c r="R13" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S13" t="n">
         <v>76.2</v>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>33.8</v>
+        <v>34.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>26.9</v>
       </c>
       <c r="R14" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S14" t="n">
         <v>44.8</v>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>31.8</v>
+        <v>32.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>28.5</v>
       </c>
       <c r="R15" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S15" t="n">
         <v>52.4</v>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>29.5</v>
+        <v>29.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>21.5</v>
       </c>
       <c r="R16" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S16" t="n">
         <v>52.4</v>
@@ -4914,12 +4914,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>28.8</v>
+        <v>29.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>21.5</v>
       </c>
       <c r="R17" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S17" t="n">
         <v>86.40000000000001</v>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.4</v>
+        <v>28.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>21.5</v>
       </c>
       <c r="R18" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S18" t="n">
         <v>64.3</v>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.2</v>
+        <v>27.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>20.1</v>
       </c>
       <c r="R19" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>54</v>
+        <v>54.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>28.5</v>
       </c>
       <c r="R3" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S3" t="n">
         <v>94.90000000000001</v>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.1</v>
+        <v>48.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>28.5</v>
       </c>
       <c r="R4" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S4" t="n">
         <v>96.59999999999999</v>
@@ -6920,12 +6920,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>47.4</v>
+        <v>47.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>21.5</v>
       </c>
       <c r="R5" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -7200,12 +7200,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.2</v>
+        <v>46.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46</v>
+        <v>46.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S7" t="n">
         <v>93.2</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>44.8</v>
+        <v>45.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>28.5</v>
       </c>
       <c r="R8" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S8" t="n">
         <v>86.40000000000001</v>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>43</v>
+        <v>43.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>26.9</v>
       </c>
       <c r="R9" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -8320,12 +8320,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>41.5</v>
+        <v>41.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>26.9</v>
       </c>
       <c r="R10" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -8600,12 +8600,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.4</v>
+        <v>38.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>28.5</v>
       </c>
       <c r="R11" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -8880,12 +8880,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>36.4</v>
+        <v>36.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>28.5</v>
       </c>
       <c r="R12" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S12" t="n">
         <v>93.2</v>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>36</v>
+        <v>36.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>21.5</v>
       </c>
       <c r="R13" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S13" t="n">
         <v>76.2</v>
@@ -9440,12 +9440,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>33.8</v>
+        <v>34.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>26.9</v>
       </c>
       <c r="R14" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S14" t="n">
         <v>44.8</v>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>31.8</v>
+        <v>32.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>28.5</v>
       </c>
       <c r="R15" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S15" t="n">
         <v>52.4</v>
@@ -10000,12 +10000,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>29.5</v>
+        <v>29.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>21.5</v>
       </c>
       <c r="R16" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S16" t="n">
         <v>52.4</v>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>28.8</v>
+        <v>29.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>21.5</v>
       </c>
       <c r="R17" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S17" t="n">
         <v>86.40000000000001</v>
@@ -10560,12 +10560,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.4</v>
+        <v>28.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>21.5</v>
       </c>
       <c r="R18" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S18" t="n">
         <v>64.3</v>
@@ -10840,12 +10840,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.2</v>
+        <v>27.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>20.1</v>
       </c>
       <c r="R19" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11120,12 +11120,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -768,11 +768,23 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>54.7</v>
+        <v>51.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -793,7 +805,7 @@
         <v>61.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R2" t="n">
         <v>27.6</v>
@@ -802,7 +814,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U2" t="n">
         <v>37.8</v>
@@ -844,7 +856,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -881,7 +893,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -954,12 +966,36 @@
           <t>0.2549</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
@@ -1008,11 +1044,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1026,14 +1074,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
         <v>48.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R3" t="n">
         <v>27.6</v>
@@ -1042,7 +1090,7 @@
         <v>95.5</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U3" t="n">
         <v>28.9</v>
@@ -1084,7 +1132,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -1121,7 +1169,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1194,12 +1242,36 @@
           <t>0.1639</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
@@ -1767,24 +1839,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -1797,14 +1869,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>46.4</v>
+        <v>43.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1818,26 +1902,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R6" t="n">
         <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1851,7 +1935,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1876,7 +1960,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1893,12 +1977,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1908,12 +1992,12 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1923,75 +2007,99 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1617</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+          <t>0.1803</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
@@ -2007,12 +2115,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2037,14 +2145,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>46.4</v>
+        <v>43.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2062,22 +2182,22 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R7" t="n">
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2091,7 +2211,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2116,7 +2236,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -2133,12 +2253,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2148,12 +2268,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2163,75 +2283,99 @@
       </c>
       